--- a/Avaliação.xlsx
+++ b/Avaliação.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CST\SOMATIVA1\APW-SOMATIVA-BACK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2227E3-D2CF-4353-8B50-68631EC55A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A0E930-633B-4D55-8064-B2BA2727FC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ENTREGAS" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="204">
   <si>
     <t>item</t>
   </si>
@@ -437,24 +437,15 @@
     <t>aluno: Lucas Santino — B1</t>
   </si>
   <si>
-    <t>aluno: Murilo Alves — B1 *** perguntas</t>
-  </si>
-  <si>
     <t>aluno: Sarah Silva — B1</t>
   </si>
   <si>
-    <t>faltou o filtro de veículo</t>
-  </si>
-  <si>
     <t>não implementou</t>
   </si>
   <si>
     <t>não implementou o model integrado com o model de usuário do django, e não registrou os models no admin</t>
   </si>
   <si>
-    <t>jwt não está funcionando</t>
-  </si>
-  <si>
     <t>aluno: Thales Godoi — B1</t>
   </si>
   <si>
@@ -470,17 +461,206 @@
     <t>Sem JWT; usa apenas cabeçalho X-Funcionario.</t>
   </si>
   <si>
-    <t>Dashboard não funcional (desconsiderado).</t>
-  </si>
-  <si>
     <t>aluno: Victor Ribeiro — B1</t>
+  </si>
+  <si>
+    <t>Regra específica para mecânico não foi implementada.</t>
+  </si>
+  <si>
+    <t>Endpoint de veículos com manutenção vencida não foi encontrado.</t>
+  </si>
+  <si>
+    <t>aluno: Murilo Alves — B1</t>
+  </si>
+  <si>
+    <t>dashboard não implementado (não funcional)</t>
+  </si>
+  <si>
+    <t>aluno: Marco Antônio - B2</t>
+  </si>
+  <si>
+    <t>Perguntas: 0.0/5.0</t>
+  </si>
+  <si>
+    <t>Perguntas: 1.0/5.0</t>
+  </si>
+  <si>
+    <t>Perguntas: 3.5/5.0</t>
+  </si>
+  <si>
+    <t>Perguntas: 3.0/5.0</t>
+  </si>
+  <si>
+    <t>Perguntas: 2.5/5.0</t>
+  </si>
+  <si>
+    <t>não traz o que foi pedido (todas as manut. Da máquina)</t>
+  </si>
+  <si>
+    <t>não filtra conforme pedido (produções reprovadas)</t>
+  </si>
+  <si>
+    <t>não implementado</t>
+  </si>
+  <si>
+    <t>outros grupos podem editar/criar produção</t>
+  </si>
+  <si>
+    <t>outros grupos podem editar/criar maquinas/manut</t>
+  </si>
+  <si>
+    <t>aluno: Victor Goes - B2</t>
+  </si>
+  <si>
+    <t>não limita a visualização</t>
+  </si>
+  <si>
+    <t>aluno: Pedro Guerra - B2</t>
+  </si>
+  <si>
+    <t>Perguntas: ???/5.0</t>
+  </si>
+  <si>
+    <t>aprox. 50</t>
+  </si>
+  <si>
+    <t>aluno: Isadora - B2</t>
+  </si>
+  <si>
+    <t>não traz as informações solicitadas, apenas id</t>
+  </si>
+  <si>
+    <t>não traz as informações solicitadas, historico de manut</t>
+  </si>
+  <si>
+    <t>aluno: Taina - B2</t>
+  </si>
+  <si>
+    <t>não finalizou implementação</t>
+  </si>
+  <si>
+    <t>incluiu autenticação mas como não finalizou, nenhum endpoint funciona</t>
+  </si>
+  <si>
+    <t>aluno: Nícolas - B3</t>
+  </si>
+  <si>
+    <t>faltou proteger acesso de manut à reserva</t>
+  </si>
+  <si>
+    <t>aluno: Leonardo - B3</t>
+  </si>
+  <si>
+    <t>retorna apenas o id do guest</t>
+  </si>
+  <si>
+    <t>faltou o funcionario responsável</t>
+  </si>
+  <si>
+    <t>criou filter mas não usou</t>
+  </si>
+  <si>
+    <t>aluno: Sarah Cruz - B3</t>
+  </si>
+  <si>
+    <t>range date não funciona</t>
+  </si>
+  <si>
+    <t>deploy não funcional</t>
+  </si>
+  <si>
+    <t>aluno: Thiago - B3</t>
+  </si>
+  <si>
+    <t>recepção pode excluir reservas</t>
+  </si>
+  <si>
+    <t>basta estar autenticado para alterar manut.</t>
+  </si>
+  <si>
+    <t>não funcional</t>
+  </si>
+  <si>
+    <t>aplicação em erro na azure</t>
+  </si>
+  <si>
+    <t>aluno: William - B3</t>
+  </si>
+  <si>
+    <t>projeto não roda</t>
+  </si>
+  <si>
+    <t>não relacionou com o user padrão do django</t>
+  </si>
+  <si>
+    <t>análise incorreta</t>
+  </si>
+  <si>
+    <t>implementado, mas não funcional</t>
+  </si>
+  <si>
+    <t>aluno: Giovanna — A1</t>
+  </si>
+  <si>
+    <t>não está trazendo os dados do funcionario</t>
+  </si>
+  <si>
+    <t>aluno: Alana  — A3</t>
+  </si>
+  <si>
+    <t>aluno: Beatriz  — A3</t>
+  </si>
+  <si>
+    <t>aluno: Gabriel Lopes  — A3</t>
+  </si>
+  <si>
+    <t>aluno: Gabriel Rosa  — A3</t>
+  </si>
+  <si>
+    <t>aluno: Gustavo Lima  — A3</t>
+  </si>
+  <si>
+    <t>aluno: Murilo Silva  — A3</t>
+  </si>
+  <si>
+    <t>web service criado mas não funcional</t>
+  </si>
+  <si>
+    <t>cb-back ok</t>
+  </si>
+  <si>
+    <t>aluno: Eduardo Costa — A1</t>
+  </si>
+  <si>
+    <t>retorna todas as informações necessárias (lote)</t>
+  </si>
+  <si>
+    <t>erro de execução</t>
+  </si>
+  <si>
+    <t>falta retornar os relacionamentos</t>
+  </si>
+  <si>
+    <t>aluno: Diogo — A1</t>
+  </si>
+  <si>
+    <t>Pergunta: 4/5</t>
+  </si>
+  <si>
+    <t>falha no cpf</t>
+  </si>
+  <si>
+    <t>aluno: Cauã — A1</t>
+  </si>
+  <si>
+    <t>Perguntas: 5/5.0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -630,8 +810,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,6 +1024,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1384,7 +1582,7 @@
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1477,6 +1675,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1489,6 +1729,24 @@
     <xf numFmtId="0" fontId="1" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="37" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="37" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1498,22 +1756,19 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1526,303 +1781,12 @@
     <xf numFmtId="0" fontId="1" fillId="37" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="37" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2182,7 +2146,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="3:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" s="31" t="s">
         <v>11</v>
       </c>
@@ -2190,7 +2154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="3:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" s="31" t="s">
         <v>12</v>
       </c>
@@ -2206,7 +2170,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="3:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" s="31" t="s">
         <v>14</v>
       </c>
@@ -2214,7 +2178,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="3:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" s="31" t="s">
         <v>15</v>
       </c>
@@ -2222,7 +2186,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="3:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" s="31" t="s">
         <v>16</v>
       </c>
@@ -2230,7 +2194,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="3:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" s="31" t="s">
         <v>17</v>
       </c>
@@ -2246,7 +2210,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="3:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" s="31" t="s">
         <v>18</v>
       </c>
@@ -2295,7 +2259,9 @@
       <c r="D20" s="12"/>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="13"/>
+      <c r="C21" s="13" t="s">
+        <v>194</v>
+      </c>
       <c r="D21" s="12"/>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
@@ -2319,7 +2285,7 @@
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="62" t="s">
+      <c r="C25" s="32" t="s">
         <v>31</v>
       </c>
       <c r="D25" s="26" t="s">
@@ -2335,7 +2301,7 @@
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="62" t="s">
+      <c r="C27" s="32" t="s">
         <v>33</v>
       </c>
       <c r="D27" s="26" t="s">
@@ -2462,7 +2428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G17"/>
+  <dimension ref="B2:G86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -2471,30 +2437,30 @@
     <col min="4" max="4" width="54" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="1"/>
     <col min="6" max="6" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="35"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="41"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -2549,7 +2515,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="53" t="s">
         <v>78</v>
       </c>
       <c r="C8" s="27">
@@ -2565,7 +2531,7 @@
       <c r="G8" s="22"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="44"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="24">
         <v>4</v>
       </c>
@@ -2579,7 +2545,7 @@
       <c r="G9" s="22"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="55" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="23">
@@ -2595,7 +2561,7 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
+      <c r="B11" s="55"/>
       <c r="C11" s="23">
         <v>6</v>
       </c>
@@ -2609,7 +2575,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="42"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -2623,7 +2589,7 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="42"/>
+      <c r="B13" s="55"/>
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -2637,7 +2603,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
+      <c r="B14" s="55"/>
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -2651,7 +2617,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="42"/>
+      <c r="B15" s="55"/>
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -2681,28 +2647,1026 @@
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
       <c r="E17" s="10">
         <f>SUM(E6:E16)</f>
         <v>100</v>
       </c>
       <c r="F17" s="10">
-        <f>SUM(F6:F8)</f>
+        <f>SUM(F6:F16)</f>
         <v>0</v>
       </c>
       <c r="G17" s="16"/>
     </row>
+    <row r="19" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="52"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="18">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="4">
+        <v>15</v>
+      </c>
+      <c r="F23" s="4">
+        <v>15</v>
+      </c>
+      <c r="G23" s="15"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E24" s="3">
+        <v>10</v>
+      </c>
+      <c r="F24" s="37">
+        <v>0</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="27">
+        <v>2</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="29">
+        <v>10</v>
+      </c>
+      <c r="F25" s="29">
+        <v>10</v>
+      </c>
+      <c r="G25" s="22"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="54"/>
+      <c r="C26" s="24">
+        <v>4</v>
+      </c>
+      <c r="D26" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="29">
+        <v>10</v>
+      </c>
+      <c r="F26" s="29">
+        <v>10</v>
+      </c>
+      <c r="G26" s="22"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="23">
+        <v>5</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E27" s="3">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3">
+        <v>5</v>
+      </c>
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="55"/>
+      <c r="C28" s="23">
+        <v>6</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="3">
+        <v>5</v>
+      </c>
+      <c r="F28" s="3">
+        <v>5</v>
+      </c>
+      <c r="G28" s="11"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="55"/>
+      <c r="C29" s="2">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="3">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3">
+        <v>5</v>
+      </c>
+      <c r="G29" s="11"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="55"/>
+      <c r="C30" s="2">
+        <v>8</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="3">
+        <v>5</v>
+      </c>
+      <c r="F30" s="3">
+        <v>5</v>
+      </c>
+      <c r="G30" s="11"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="55"/>
+      <c r="C31" s="2">
+        <v>9</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E31" s="3">
+        <v>15</v>
+      </c>
+      <c r="F31" s="3">
+        <v>15</v>
+      </c>
+      <c r="G31" s="11"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="55"/>
+      <c r="C32" s="2">
+        <v>10</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E32" s="3">
+        <v>15</v>
+      </c>
+      <c r="F32" s="37">
+        <v>0</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="30">
+        <v>2</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="4">
+        <v>5</v>
+      </c>
+      <c r="F33" s="4">
+        <v>5</v>
+      </c>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="57"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="10">
+        <f>SUM(E23:E33)</f>
+        <v>100</v>
+      </c>
+      <c r="F34" s="33">
+        <f>SUM(F23:F33)</f>
+        <v>75</v>
+      </c>
+      <c r="G34" s="34" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="C37" s="47"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="49"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="52"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="18">
+        <v>1</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E40" s="4">
+        <v>15</v>
+      </c>
+      <c r="F40" s="44">
+        <v>15</v>
+      </c>
+      <c r="G40" s="15"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10</v>
+      </c>
+      <c r="F41" s="37">
+        <v>0</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" s="27">
+        <v>2</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" s="29">
+        <v>10</v>
+      </c>
+      <c r="F42" s="38">
+        <v>5</v>
+      </c>
+      <c r="G42" s="22" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="54"/>
+      <c r="C43" s="24">
+        <v>4</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" s="29">
+        <v>10</v>
+      </c>
+      <c r="F43" s="43">
+        <v>0</v>
+      </c>
+      <c r="G43" s="22"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="23">
+        <v>5</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5</v>
+      </c>
+      <c r="F44" s="41">
+        <v>5</v>
+      </c>
+      <c r="G44" s="11"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="55"/>
+      <c r="C45" s="23">
+        <v>6</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5</v>
+      </c>
+      <c r="F45" s="41">
+        <v>5</v>
+      </c>
+      <c r="G45" s="11"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="55"/>
+      <c r="C46" s="2">
+        <v>7</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5</v>
+      </c>
+      <c r="F46" s="41">
+        <v>5</v>
+      </c>
+      <c r="G46" s="11"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="55"/>
+      <c r="C47" s="2">
+        <v>8</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E47" s="3">
+        <v>5</v>
+      </c>
+      <c r="F47" s="41">
+        <v>5</v>
+      </c>
+      <c r="G47" s="11"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="55"/>
+      <c r="C48" s="2">
+        <v>9</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E48" s="3">
+        <v>15</v>
+      </c>
+      <c r="F48" s="41">
+        <v>15</v>
+      </c>
+      <c r="G48" s="11"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="55"/>
+      <c r="C49" s="2">
+        <v>10</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E49" s="3">
+        <v>15</v>
+      </c>
+      <c r="F49" s="41">
+        <v>0</v>
+      </c>
+      <c r="G49" s="11"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="30">
+        <v>2</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E50" s="4">
+        <v>5</v>
+      </c>
+      <c r="F50" s="44">
+        <v>5</v>
+      </c>
+      <c r="G50" s="15"/>
+    </row>
+    <row r="51" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="57"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="10">
+        <f>SUM(E40:E50)</f>
+        <v>100</v>
+      </c>
+      <c r="F51" s="33">
+        <f>SUM(F40:F50)</f>
+        <v>60</v>
+      </c>
+      <c r="G51" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B54" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="C54" s="47"/>
+      <c r="D54" s="48"/>
+      <c r="E54" s="48"/>
+      <c r="F54" s="48"/>
+      <c r="G54" s="49"/>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="51"/>
+      <c r="D55" s="51"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="51"/>
+      <c r="G55" s="52"/>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="18">
+        <v>1</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E57" s="4">
+        <v>15</v>
+      </c>
+      <c r="F57" s="44">
+        <v>15</v>
+      </c>
+      <c r="G57" s="15"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E58" s="3">
+        <v>10</v>
+      </c>
+      <c r="F58" s="41">
+        <v>10</v>
+      </c>
+      <c r="G58" s="11"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59" s="27">
+        <v>2</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E59" s="29">
+        <v>10</v>
+      </c>
+      <c r="F59" s="38">
+        <v>5</v>
+      </c>
+      <c r="G59" s="22" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="54"/>
+      <c r="C60" s="24">
+        <v>4</v>
+      </c>
+      <c r="D60" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E60" s="29">
+        <v>10</v>
+      </c>
+      <c r="F60" s="43">
+        <v>10</v>
+      </c>
+      <c r="G60" s="22"/>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B61" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C61" s="23">
+        <v>5</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5</v>
+      </c>
+      <c r="F61" s="41">
+        <v>5</v>
+      </c>
+      <c r="G61" s="11"/>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="55"/>
+      <c r="C62" s="23">
+        <v>6</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5</v>
+      </c>
+      <c r="F62" s="41">
+        <v>5</v>
+      </c>
+      <c r="G62" s="11"/>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B63" s="55"/>
+      <c r="C63" s="2">
+        <v>7</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E63" s="3">
+        <v>5</v>
+      </c>
+      <c r="F63" s="41">
+        <v>5</v>
+      </c>
+      <c r="G63" s="11"/>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B64" s="55"/>
+      <c r="C64" s="2">
+        <v>8</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E64" s="3">
+        <v>5</v>
+      </c>
+      <c r="F64" s="41">
+        <v>5</v>
+      </c>
+      <c r="G64" s="11"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="55"/>
+      <c r="C65" s="2">
+        <v>9</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E65" s="3">
+        <v>15</v>
+      </c>
+      <c r="F65" s="41">
+        <v>15</v>
+      </c>
+      <c r="G65" s="11"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="55"/>
+      <c r="C66" s="2">
+        <v>10</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E66" s="3">
+        <v>15</v>
+      </c>
+      <c r="F66" s="41">
+        <v>15</v>
+      </c>
+      <c r="G66" s="11"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" s="30">
+        <v>2</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E67" s="4">
+        <v>5</v>
+      </c>
+      <c r="F67" s="44">
+        <v>5</v>
+      </c>
+      <c r="G67" s="15"/>
+    </row>
+    <row r="68" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="57"/>
+      <c r="D68" s="58"/>
+      <c r="E68" s="10">
+        <f>SUM(E57:E67)</f>
+        <v>100</v>
+      </c>
+      <c r="F68" s="33">
+        <f>SUM(F57:F67)</f>
+        <v>95</v>
+      </c>
+      <c r="G68" s="34" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B72" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="C72" s="47"/>
+      <c r="D72" s="48"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="48"/>
+      <c r="G72" s="49"/>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B73" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="51"/>
+      <c r="D73" s="51"/>
+      <c r="E73" s="51"/>
+      <c r="F73" s="51"/>
+      <c r="G73" s="52"/>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B74" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B75" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C75" s="18">
+        <v>1</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E75" s="4">
+        <v>15</v>
+      </c>
+      <c r="F75" s="44">
+        <v>15</v>
+      </c>
+      <c r="G75" s="15"/>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10</v>
+      </c>
+      <c r="F76" s="41">
+        <v>10</v>
+      </c>
+      <c r="G76" s="11"/>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" s="27">
+        <v>2</v>
+      </c>
+      <c r="D77" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E77" s="29">
+        <v>10</v>
+      </c>
+      <c r="F77" s="43">
+        <v>10</v>
+      </c>
+      <c r="G77" s="22"/>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="54"/>
+      <c r="C78" s="24">
+        <v>4</v>
+      </c>
+      <c r="D78" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E78" s="29">
+        <v>10</v>
+      </c>
+      <c r="F78" s="43">
+        <v>10</v>
+      </c>
+      <c r="G78" s="22"/>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C79" s="23">
+        <v>5</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E79" s="3">
+        <v>5</v>
+      </c>
+      <c r="F79" s="41">
+        <v>5</v>
+      </c>
+      <c r="G79" s="11"/>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="55"/>
+      <c r="C80" s="23">
+        <v>6</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E80" s="3">
+        <v>5</v>
+      </c>
+      <c r="F80" s="41"/>
+      <c r="G80" s="11"/>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B81" s="55"/>
+      <c r="C81" s="2">
+        <v>7</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E81" s="3">
+        <v>5</v>
+      </c>
+      <c r="F81" s="41"/>
+      <c r="G81" s="11"/>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="55"/>
+      <c r="C82" s="2">
+        <v>8</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E82" s="3">
+        <v>5</v>
+      </c>
+      <c r="F82" s="41"/>
+      <c r="G82" s="11"/>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B83" s="55"/>
+      <c r="C83" s="2">
+        <v>9</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E83" s="3">
+        <v>15</v>
+      </c>
+      <c r="F83" s="41"/>
+      <c r="G83" s="11"/>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B84" s="55"/>
+      <c r="C84" s="2">
+        <v>10</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E84" s="3">
+        <v>15</v>
+      </c>
+      <c r="F84" s="41"/>
+      <c r="G84" s="11"/>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B85" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C85" s="30">
+        <v>2</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E85" s="4">
+        <v>5</v>
+      </c>
+      <c r="F85" s="44"/>
+      <c r="G85" s="15"/>
+    </row>
+    <row r="86" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C86" s="57"/>
+      <c r="D86" s="58"/>
+      <c r="E86" s="10">
+        <f>SUM(E75:E85)</f>
+        <v>100</v>
+      </c>
+      <c r="F86" s="45">
+        <f>SUM(F75:F85)</f>
+        <v>50</v>
+      </c>
+      <c r="G86" s="34" t="s">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="25">
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B10:B15"/>
     <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B27:B32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B49"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="B61:B66"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="B79:B84"/>
+    <mergeCell ref="B86:D86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2726,24 +3690,24 @@
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="35"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="41"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -2782,7 +3746,7 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="64" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="23" t="s">
@@ -2798,7 +3762,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="59"/>
+      <c r="B8" s="65"/>
       <c r="C8" s="23" t="s">
         <v>89</v>
       </c>
@@ -2812,7 +3776,7 @@
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="53" t="s">
         <v>78</v>
       </c>
       <c r="C9" s="27">
@@ -2828,7 +3792,7 @@
       <c r="G9" s="22"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="44"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="24">
         <v>5</v>
       </c>
@@ -2842,7 +3806,7 @@
       <c r="G10" s="22"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="55" t="s">
         <v>75</v>
       </c>
       <c r="C11" s="23">
@@ -2858,7 +3822,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="42"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -2872,7 +3836,7 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="42"/>
+      <c r="B13" s="55"/>
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -2886,7 +3850,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
+      <c r="B14" s="55"/>
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -2900,7 +3864,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="42"/>
+      <c r="B15" s="55"/>
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -2930,11 +3894,11 @@
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
       <c r="E17" s="10">
         <f>SUM(E6:E16)</f>
         <v>100</v>
@@ -2947,24 +3911,24 @@
     </row>
     <row r="19" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="67"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="49"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="70"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
@@ -3005,7 +3969,7 @@
       <c r="G23" s="15"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="57" t="s">
+      <c r="B24" s="62" t="s">
         <v>71</v>
       </c>
       <c r="C24" s="23" t="s">
@@ -3023,7 +3987,7 @@
       <c r="G24" s="11"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="51"/>
+      <c r="B25" s="63"/>
       <c r="C25" s="23" t="s">
         <v>89</v>
       </c>
@@ -3041,7 +4005,7 @@
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="50" t="s">
+      <c r="B26" s="71" t="s">
         <v>78</v>
       </c>
       <c r="C26" s="27">
@@ -3059,7 +4023,7 @@
       <c r="G26" s="22"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="51"/>
+      <c r="B27" s="63"/>
       <c r="C27" s="24">
         <v>5</v>
       </c>
@@ -3077,7 +4041,7 @@
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="55" t="s">
         <v>75</v>
       </c>
       <c r="C28" s="23">
@@ -3097,7 +4061,7 @@
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="52"/>
+      <c r="B29" s="72"/>
       <c r="C29" s="2">
         <v>7</v>
       </c>
@@ -3115,7 +4079,7 @@
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="52"/>
+      <c r="B30" s="72"/>
       <c r="C30" s="2">
         <v>8</v>
       </c>
@@ -3133,7 +4097,7 @@
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="52"/>
+      <c r="B31" s="72"/>
       <c r="C31" s="2">
         <v>9</v>
       </c>
@@ -3151,7 +4115,7 @@
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="53"/>
+      <c r="B32" s="73"/>
       <c r="C32" s="2">
         <v>10</v>
       </c>
@@ -3185,11 +4149,11 @@
       <c r="G33" s="15"/>
     </row>
     <row r="34" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="54" t="s">
+      <c r="B34" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="55"/>
-      <c r="D34" s="56"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="61"/>
       <c r="E34" s="10" t="s">
         <v>111</v>
       </c>
@@ -3200,6 +4164,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B28:B32"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="B4:G4"/>
@@ -3207,11 +4176,6 @@
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B15"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B28:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3220,7 +4184,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80347C0-EA69-44D2-B1EB-4BDE3841A27B}">
-  <dimension ref="B2:G17"/>
+  <dimension ref="B2:G122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3229,30 +4193,30 @@
     <col min="4" max="4" width="54" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="1"/>
     <col min="6" max="6" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="36.28515625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="35"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="41"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -3291,7 +4255,7 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="64" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="23" t="s">
@@ -3307,7 +4271,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="60"/>
+      <c r="B8" s="74"/>
       <c r="C8" s="23" t="s">
         <v>89</v>
       </c>
@@ -3321,7 +4285,7 @@
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="59"/>
+      <c r="B9" s="65"/>
       <c r="C9" s="23" t="s">
         <v>96</v>
       </c>
@@ -3335,7 +4299,7 @@
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="53" t="s">
         <v>78</v>
       </c>
       <c r="C10" s="25">
@@ -3351,7 +4315,7 @@
       <c r="G10" s="22"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="61"/>
+      <c r="B11" s="75"/>
       <c r="C11" s="25">
         <v>6</v>
       </c>
@@ -3365,7 +4329,7 @@
       <c r="G11" s="22"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="44"/>
+      <c r="B12" s="54"/>
       <c r="C12" s="24">
         <v>7</v>
       </c>
@@ -3379,7 +4343,7 @@
       <c r="G12" s="22"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="55" t="s">
         <v>75</v>
       </c>
       <c r="C13" s="23">
@@ -3395,7 +4359,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
+      <c r="B14" s="55"/>
       <c r="C14" s="2">
         <v>10</v>
       </c>
@@ -3441,11 +4405,11 @@
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
       <c r="E17" s="10">
         <f>SUM(E6:E16)</f>
         <v>100</v>
@@ -3454,16 +4418,1422 @@
         <f>SUM(F6:F10)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="16"/>
+      <c r="G17" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" s="47"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="52"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="18">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="4">
+        <v>15</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="15"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="3">
+        <v>5</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="74"/>
+      <c r="C26" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="11"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="65"/>
+      <c r="C27" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="3">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="25">
+        <v>2</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="29">
+        <v>10</v>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="22"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="75"/>
+      <c r="C29" s="25">
+        <v>6</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="29">
+        <v>5</v>
+      </c>
+      <c r="F29" s="29"/>
+      <c r="G29" s="22"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="54"/>
+      <c r="C30" s="24">
+        <v>7</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" s="29">
+        <v>5</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="22"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="23">
+        <v>6</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="3">
+        <v>10</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="11"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="55"/>
+      <c r="C32" s="2">
+        <v>10</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="3">
+        <v>15</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="11"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="30">
+        <v>9</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E33" s="4">
+        <v>5</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="2">
+        <v>11</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="3">
+        <v>20</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0</v>
+      </c>
+      <c r="G34" s="11"/>
+    </row>
+    <row r="35" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="57"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="10">
+        <f>SUM(E24:E34)</f>
+        <v>100</v>
+      </c>
+      <c r="F35" s="10">
+        <f>SUM(F24:F28)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="C39" s="47"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="49"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="52"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="18">
+        <v>1</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E42" s="4">
+        <v>15</v>
+      </c>
+      <c r="F42" s="4"/>
+      <c r="G42" s="15"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="11"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="74"/>
+      <c r="C44" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="11"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="65"/>
+      <c r="C45" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="11"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C46" s="25">
+        <v>2</v>
+      </c>
+      <c r="D46" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="29">
+        <v>10</v>
+      </c>
+      <c r="F46" s="29"/>
+      <c r="G46" s="22"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="75"/>
+      <c r="C47" s="25">
+        <v>6</v>
+      </c>
+      <c r="D47" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" s="29">
+        <v>5</v>
+      </c>
+      <c r="F47" s="29"/>
+      <c r="G47" s="22"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="54"/>
+      <c r="C48" s="24">
+        <v>7</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E48" s="29">
+        <v>5</v>
+      </c>
+      <c r="F48" s="29"/>
+      <c r="G48" s="22"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="23">
+        <v>6</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="11"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="55"/>
+      <c r="C50" s="2">
+        <v>10</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50" s="3">
+        <v>15</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="11"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="30">
+        <v>9</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E51" s="4">
+        <v>5</v>
+      </c>
+      <c r="F51" s="4"/>
+      <c r="G51" s="15"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" s="2">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E52" s="3">
+        <v>20</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="11"/>
+    </row>
+    <row r="53" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="57"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="10">
+        <f>SUM(E42:E52)</f>
+        <v>100</v>
+      </c>
+      <c r="F53" s="10">
+        <f>SUM(F42:F46)</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="C56" s="47"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="49"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="51"/>
+      <c r="D57" s="51"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="51"/>
+      <c r="G57" s="52"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="18">
+        <v>1</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" s="4">
+        <v>15</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="15"/>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3"/>
+      <c r="G60" s="11"/>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B61" s="74"/>
+      <c r="C61" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5</v>
+      </c>
+      <c r="F61" s="3"/>
+      <c r="G61" s="11"/>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="65"/>
+      <c r="C62" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="11"/>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B63" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" s="25">
+        <v>2</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E63" s="29">
+        <v>10</v>
+      </c>
+      <c r="F63" s="29"/>
+      <c r="G63" s="22"/>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B64" s="75"/>
+      <c r="C64" s="25">
+        <v>6</v>
+      </c>
+      <c r="D64" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E64" s="29">
+        <v>5</v>
+      </c>
+      <c r="F64" s="29"/>
+      <c r="G64" s="22"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="54"/>
+      <c r="C65" s="24">
+        <v>7</v>
+      </c>
+      <c r="D65" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E65" s="29">
+        <v>5</v>
+      </c>
+      <c r="F65" s="29"/>
+      <c r="G65" s="22"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66" s="23">
+        <v>6</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10</v>
+      </c>
+      <c r="F66" s="3"/>
+      <c r="G66" s="11"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="55"/>
+      <c r="C67" s="2">
+        <v>10</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E67" s="3">
+        <v>15</v>
+      </c>
+      <c r="F67" s="3"/>
+      <c r="G67" s="11"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="30">
+        <v>9</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E68" s="4">
+        <v>5</v>
+      </c>
+      <c r="F68" s="4"/>
+      <c r="G68" s="15"/>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" s="2">
+        <v>11</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E69" s="3">
+        <v>20</v>
+      </c>
+      <c r="F69" s="37">
+        <v>5</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="57"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="10">
+        <f>SUM(E59:E69)</f>
+        <v>100</v>
+      </c>
+      <c r="F70" s="10">
+        <f>SUM(F59:F63)</f>
+        <v>0</v>
+      </c>
+      <c r="G70" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B73" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="C73" s="47"/>
+      <c r="D73" s="48"/>
+      <c r="E73" s="48"/>
+      <c r="F73" s="48"/>
+      <c r="G73" s="49"/>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B74" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="51"/>
+      <c r="D74" s="51"/>
+      <c r="E74" s="51"/>
+      <c r="F74" s="51"/>
+      <c r="G74" s="52"/>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B75" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C76" s="18">
+        <v>1</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E76" s="4">
+        <v>15</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="15"/>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E77" s="3">
+        <v>5</v>
+      </c>
+      <c r="F77" s="3"/>
+      <c r="G77" s="11"/>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="74"/>
+      <c r="C78" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E78" s="3">
+        <v>5</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="11"/>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="65"/>
+      <c r="C79" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E79" s="3">
+        <v>5</v>
+      </c>
+      <c r="F79" s="3"/>
+      <c r="G79" s="11"/>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C80" s="25">
+        <v>2</v>
+      </c>
+      <c r="D80" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E80" s="29">
+        <v>10</v>
+      </c>
+      <c r="F80" s="29"/>
+      <c r="G80" s="22"/>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B81" s="75"/>
+      <c r="C81" s="25">
+        <v>6</v>
+      </c>
+      <c r="D81" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E81" s="29">
+        <v>5</v>
+      </c>
+      <c r="F81" s="29"/>
+      <c r="G81" s="22"/>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="54"/>
+      <c r="C82" s="24">
+        <v>7</v>
+      </c>
+      <c r="D82" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E82" s="29">
+        <v>5</v>
+      </c>
+      <c r="F82" s="29"/>
+      <c r="G82" s="22"/>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B83" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C83" s="23">
+        <v>6</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>10</v>
+      </c>
+      <c r="F83" s="3"/>
+      <c r="G83" s="11"/>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B84" s="55"/>
+      <c r="C84" s="2">
+        <v>10</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E84" s="3">
+        <v>15</v>
+      </c>
+      <c r="F84" s="3"/>
+      <c r="G84" s="11"/>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B85" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C85" s="30">
+        <v>9</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E85" s="4">
+        <v>5</v>
+      </c>
+      <c r="F85" s="4"/>
+      <c r="G85" s="15"/>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B86" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C86" s="2">
+        <v>11</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E86" s="3">
+        <v>20</v>
+      </c>
+      <c r="F86" s="37">
+        <v>5</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" s="57"/>
+      <c r="D87" s="58"/>
+      <c r="E87" s="10">
+        <f>SUM(E76:E86)</f>
+        <v>100</v>
+      </c>
+      <c r="F87" s="10">
+        <f>SUM(F76:F80)</f>
+        <v>0</v>
+      </c>
+      <c r="G87" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B90" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="C90" s="47"/>
+      <c r="D90" s="48"/>
+      <c r="E90" s="48"/>
+      <c r="F90" s="48"/>
+      <c r="G90" s="49"/>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B91" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="51"/>
+      <c r="D91" s="51"/>
+      <c r="E91" s="51"/>
+      <c r="F91" s="51"/>
+      <c r="G91" s="52"/>
+    </row>
+    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B92" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C92" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G92" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B93" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C93" s="18">
+        <v>1</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E93" s="4">
+        <v>15</v>
+      </c>
+      <c r="F93" s="4"/>
+      <c r="G93" s="15"/>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B94" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C94" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E94" s="3">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="11"/>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B95" s="74"/>
+      <c r="C95" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E95" s="3">
+        <v>5</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="11"/>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B96" s="65"/>
+      <c r="C96" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E96" s="3">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="11"/>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B97" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C97" s="25">
+        <v>2</v>
+      </c>
+      <c r="D97" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E97" s="29">
+        <v>10</v>
+      </c>
+      <c r="F97" s="29"/>
+      <c r="G97" s="22"/>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B98" s="75"/>
+      <c r="C98" s="25">
+        <v>6</v>
+      </c>
+      <c r="D98" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E98" s="29">
+        <v>5</v>
+      </c>
+      <c r="F98" s="29"/>
+      <c r="G98" s="22"/>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B99" s="54"/>
+      <c r="C99" s="24">
+        <v>7</v>
+      </c>
+      <c r="D99" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E99" s="29">
+        <v>5</v>
+      </c>
+      <c r="F99" s="29"/>
+      <c r="G99" s="22"/>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B100" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C100" s="23">
+        <v>6</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>10</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="11"/>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B101" s="55"/>
+      <c r="C101" s="2">
+        <v>10</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E101" s="3">
+        <v>15</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="11"/>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B102" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C102" s="30">
+        <v>9</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E102" s="4">
+        <v>5</v>
+      </c>
+      <c r="F102" s="4"/>
+      <c r="G102" s="15"/>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B103" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C103" s="2">
+        <v>11</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E103" s="3">
+        <v>20</v>
+      </c>
+      <c r="F103" s="3">
+        <v>0</v>
+      </c>
+      <c r="G103" s="11"/>
+    </row>
+    <row r="104" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C104" s="57"/>
+      <c r="D104" s="58"/>
+      <c r="E104" s="10">
+        <f>SUM(E93:E103)</f>
+        <v>100</v>
+      </c>
+      <c r="F104" s="10">
+        <f>SUM(F93:F97)</f>
+        <v>0</v>
+      </c>
+      <c r="G104" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B108" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="C108" s="47"/>
+      <c r="D108" s="48"/>
+      <c r="E108" s="48"/>
+      <c r="F108" s="48"/>
+      <c r="G108" s="49"/>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B109" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="51"/>
+      <c r="D109" s="51"/>
+      <c r="E109" s="51"/>
+      <c r="F109" s="51"/>
+      <c r="G109" s="52"/>
+    </row>
+    <row r="110" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B110" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C110" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G110" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B111" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="18">
+        <v>1</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E111" s="4">
+        <v>15</v>
+      </c>
+      <c r="F111" s="4"/>
+      <c r="G111" s="15"/>
+    </row>
+    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B112" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C112" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E112" s="3">
+        <v>5</v>
+      </c>
+      <c r="F112" s="3"/>
+      <c r="G112" s="11"/>
+    </row>
+    <row r="113" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B113" s="74"/>
+      <c r="C113" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E113" s="3">
+        <v>5</v>
+      </c>
+      <c r="F113" s="3"/>
+      <c r="G113" s="11"/>
+    </row>
+    <row r="114" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B114" s="65"/>
+      <c r="C114" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E114" s="3">
+        <v>5</v>
+      </c>
+      <c r="F114" s="3"/>
+      <c r="G114" s="11"/>
+    </row>
+    <row r="115" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B115" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C115" s="25">
+        <v>2</v>
+      </c>
+      <c r="D115" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E115" s="29">
+        <v>10</v>
+      </c>
+      <c r="F115" s="29"/>
+      <c r="G115" s="22"/>
+    </row>
+    <row r="116" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B116" s="75"/>
+      <c r="C116" s="25">
+        <v>6</v>
+      </c>
+      <c r="D116" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E116" s="29">
+        <v>5</v>
+      </c>
+      <c r="F116" s="29"/>
+      <c r="G116" s="22"/>
+    </row>
+    <row r="117" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B117" s="54"/>
+      <c r="C117" s="24">
+        <v>7</v>
+      </c>
+      <c r="D117" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E117" s="29">
+        <v>5</v>
+      </c>
+      <c r="F117" s="29"/>
+      <c r="G117" s="22"/>
+    </row>
+    <row r="118" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B118" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C118" s="23">
+        <v>6</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E118" s="3">
+        <v>10</v>
+      </c>
+      <c r="F118" s="3"/>
+      <c r="G118" s="11"/>
+    </row>
+    <row r="119" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B119" s="55"/>
+      <c r="C119" s="2">
+        <v>10</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E119" s="3">
+        <v>15</v>
+      </c>
+      <c r="F119" s="3"/>
+      <c r="G119" s="11"/>
+    </row>
+    <row r="120" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B120" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C120" s="30">
+        <v>9</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E120" s="4">
+        <v>5</v>
+      </c>
+      <c r="F120" s="4"/>
+      <c r="G120" s="15"/>
+    </row>
+    <row r="121" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B121" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C121" s="2">
+        <v>11</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E121" s="3">
+        <v>20</v>
+      </c>
+      <c r="F121" s="37">
+        <v>5</v>
+      </c>
+      <c r="G121" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C122" s="57"/>
+      <c r="D122" s="58"/>
+      <c r="E122" s="10">
+        <f>SUM(E111:E121)</f>
+        <v>100</v>
+      </c>
+      <c r="F122" s="10">
+        <f>SUM(F111:F115)</f>
+        <v>0</v>
+      </c>
+      <c r="G122" s="39" t="s">
+        <v>158</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="42">
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="B90:G90"/>
+    <mergeCell ref="B91:G91"/>
+    <mergeCell ref="B94:B96"/>
+    <mergeCell ref="B97:B99"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B108:G108"/>
+    <mergeCell ref="B109:G109"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="B118:B119"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3487,24 +5857,24 @@
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="35"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="41"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -3559,7 +5929,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="53" t="s">
         <v>78</v>
       </c>
       <c r="C8" s="27">
@@ -3575,7 +5945,7 @@
       <c r="G8" s="22"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="44"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="24">
         <v>4</v>
       </c>
@@ -3589,7 +5959,7 @@
       <c r="G9" s="22"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="55" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="23">
@@ -3605,7 +5975,7 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
+      <c r="B11" s="55"/>
       <c r="C11" s="23">
         <v>6</v>
       </c>
@@ -3619,7 +5989,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="42"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -3633,7 +6003,7 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="42"/>
+      <c r="B13" s="55"/>
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -3647,7 +6017,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
+      <c r="B14" s="55"/>
       <c r="C14" s="2">
         <v>10</v>
       </c>
@@ -3660,22 +6030,22 @@
       <c r="F14" s="3"/>
       <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="2:7" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="42"/>
-      <c r="C15" s="114">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="55"/>
+      <c r="C15" s="2">
         <v>8</v>
       </c>
-      <c r="D15" s="115" t="s">
-        <v>140</v>
-      </c>
-      <c r="E15" s="115">
+      <c r="D15" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E15" s="3">
         <v>15</v>
       </c>
-      <c r="F15" s="115"/>
-      <c r="G15" s="120"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="42"/>
+      <c r="B16" s="55"/>
       <c r="C16" s="2">
         <v>9</v>
       </c>
@@ -3705,11 +6075,11 @@
       <c r="G17" s="15"/>
     </row>
     <row r="18" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="58"/>
       <c r="E18" s="10">
         <f>SUM(E6:E17)</f>
         <v>100</v>
@@ -3722,1342 +6092,1369 @@
     </row>
     <row r="21" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="67"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="49"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="70"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="138" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="147" t="s">
+      <c r="B24" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="134" t="s">
+      <c r="D24" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="134" t="s">
+      <c r="E24" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F24" s="134" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="141" t="s">
+      <c r="F24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="145" t="s">
+      <c r="B25" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="144">
+      <c r="C25" s="18">
         <v>1</v>
       </c>
-      <c r="D25" s="136" t="s">
+      <c r="D25" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="136">
+      <c r="E25" s="4">
         <v>15</v>
       </c>
-      <c r="F25" s="136">
+      <c r="F25" s="4">
         <v>15</v>
       </c>
-      <c r="G25" s="142"/>
+      <c r="G25" s="15"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="137" t="s">
+      <c r="B26" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="149" t="s">
+      <c r="C26" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="D26" s="135" t="s">
+      <c r="D26" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="135">
-        <v>10</v>
-      </c>
-      <c r="F26" s="135">
-        <v>10</v>
-      </c>
-      <c r="G26" s="140"/>
+      <c r="E26" s="3">
+        <v>10</v>
+      </c>
+      <c r="F26" s="3">
+        <v>10</v>
+      </c>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="50" t="s">
+      <c r="B27" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="151">
+      <c r="C27" s="27">
         <v>2</v>
       </c>
-      <c r="D27" s="152" t="s">
+      <c r="D27" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="E27" s="152">
-        <v>10</v>
-      </c>
-      <c r="F27" s="152">
-        <v>10</v>
-      </c>
-      <c r="G27" s="148"/>
+      <c r="E27" s="29">
+        <v>10</v>
+      </c>
+      <c r="F27" s="29">
+        <v>10</v>
+      </c>
+      <c r="G27" s="22"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="51"/>
-      <c r="C28" s="150">
+      <c r="B28" s="63"/>
+      <c r="C28" s="24">
         <v>4</v>
       </c>
-      <c r="D28" s="152" t="s">
+      <c r="D28" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="152">
-        <v>10</v>
-      </c>
-      <c r="F28" s="152">
-        <v>10</v>
-      </c>
-      <c r="G28" s="148"/>
+      <c r="E28" s="29">
+        <v>10</v>
+      </c>
+      <c r="F28" s="29">
+        <v>10</v>
+      </c>
+      <c r="G28" s="22"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
+      <c r="B29" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="149">
-        <v>5</v>
-      </c>
-      <c r="D29" s="135" t="s">
+      <c r="C29" s="23">
+        <v>5</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E29" s="135">
-        <v>5</v>
-      </c>
-      <c r="F29" s="135">
-        <v>5</v>
-      </c>
-      <c r="G29" s="140"/>
+      <c r="E29" s="3">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3">
+        <v>5</v>
+      </c>
+      <c r="G29" s="11"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="52"/>
-      <c r="C30" s="149">
+      <c r="B30" s="72"/>
+      <c r="C30" s="23">
         <v>6</v>
       </c>
-      <c r="D30" s="135" t="s">
+      <c r="D30" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E30" s="135">
-        <v>5</v>
-      </c>
-      <c r="F30" s="135">
-        <v>5</v>
-      </c>
-      <c r="G30" s="140"/>
+      <c r="E30" s="3">
+        <v>5</v>
+      </c>
+      <c r="F30" s="3">
+        <v>5</v>
+      </c>
+      <c r="G30" s="11"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="52"/>
-      <c r="C31" s="134">
+      <c r="B31" s="72"/>
+      <c r="C31" s="2">
         <v>7</v>
       </c>
-      <c r="D31" s="135" t="s">
+      <c r="D31" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="135">
-        <v>5</v>
-      </c>
-      <c r="F31" s="135">
-        <v>5</v>
-      </c>
-      <c r="G31" s="140"/>
+      <c r="E31" s="3">
+        <v>5</v>
+      </c>
+      <c r="F31" s="3">
+        <v>5</v>
+      </c>
+      <c r="G31" s="11"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="52"/>
-      <c r="C32" s="134">
+      <c r="B32" s="72"/>
+      <c r="C32" s="2">
         <v>8</v>
       </c>
-      <c r="D32" s="135" t="s">
+      <c r="D32" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="135">
-        <v>5</v>
-      </c>
-      <c r="F32" s="135">
-        <v>5</v>
-      </c>
-      <c r="G32" s="140"/>
+      <c r="E32" s="3">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
+        <v>5</v>
+      </c>
+      <c r="G32" s="11"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="52"/>
-      <c r="C33" s="134">
-        <v>10</v>
-      </c>
-      <c r="D33" s="135" t="s">
+      <c r="B33" s="72"/>
+      <c r="C33" s="2">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E33" s="135">
-        <v>5</v>
-      </c>
-      <c r="F33" s="135">
-        <v>10</v>
-      </c>
-      <c r="G33" s="140"/>
+      <c r="E33" s="3">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
+        <v>5</v>
+      </c>
+      <c r="G33" s="11"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="52"/>
-      <c r="C34" s="134">
+      <c r="B34" s="72"/>
+      <c r="C34" s="2">
         <v>8</v>
       </c>
-      <c r="D34" s="135" t="s">
-        <v>140</v>
-      </c>
-      <c r="E34" s="135">
+      <c r="D34" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="3">
         <v>15</v>
       </c>
-      <c r="F34" s="135">
-        <v>10</v>
-      </c>
-      <c r="G34" s="140"/>
+      <c r="F34" s="3">
+        <v>15</v>
+      </c>
+      <c r="G34" s="11"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="53"/>
-      <c r="C35" s="134">
+      <c r="B35" s="73"/>
+      <c r="C35" s="2">
         <v>9</v>
       </c>
-      <c r="D35" s="135" t="s">
+      <c r="D35" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E35" s="135">
-        <v>10</v>
-      </c>
-      <c r="F35" s="135">
-        <v>10</v>
-      </c>
-      <c r="G35" s="140"/>
+      <c r="E35" s="3">
+        <v>10</v>
+      </c>
+      <c r="F35" s="3">
+        <v>10</v>
+      </c>
+      <c r="G35" s="11"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="146" t="s">
+      <c r="B36" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="153">
+      <c r="C36" s="30">
         <v>2</v>
       </c>
-      <c r="D36" s="136" t="s">
+      <c r="D36" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E36" s="136">
-        <v>5</v>
-      </c>
-      <c r="F36" s="136">
-        <v>0</v>
-      </c>
-      <c r="G36" s="142" t="s">
-        <v>141</v>
+      <c r="E36" s="4">
+        <v>5</v>
+      </c>
+      <c r="F36" s="36">
+        <v>0</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="54" t="s">
+      <c r="B37" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C37" s="55"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="139">
+      <c r="C37" s="60"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="10">
         <f>SUM(E25:E36)</f>
         <v>100</v>
       </c>
-      <c r="F37" s="139">
+      <c r="F37" s="33">
         <f>SUM(F25:F36)</f>
         <v>95</v>
       </c>
-      <c r="G37" s="143"/>
-    </row>
-    <row r="38" spans="2:7" s="133" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="G37" s="34" t="s">
+        <v>148</v>
+      </c>
+    </row>
     <row r="39" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B40" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="46"/>
+      <c r="B40" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="67"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="47" t="s">
+      <c r="B41" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="49"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="70"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="C42" s="74" t="s">
+      <c r="B42" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D42" s="63" t="s">
+      <c r="D42" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="63" t="s">
+      <c r="E42" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F42" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="G42" s="69" t="s">
+      <c r="F42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G42" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="72" t="s">
+      <c r="B43" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C43" s="71">
+      <c r="C43" s="18">
         <v>1</v>
       </c>
-      <c r="D43" s="65" t="s">
+      <c r="D43" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E43" s="136">
+      <c r="E43" s="4">
         <v>15</v>
       </c>
-      <c r="F43" s="81">
+      <c r="F43" s="4">
         <v>15</v>
       </c>
-      <c r="G43" s="83"/>
+      <c r="G43" s="15"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="66" t="s">
+      <c r="B44" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C44" s="75" t="s">
+      <c r="C44" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="D44" s="64" t="s">
+      <c r="D44" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E44" s="135">
-        <v>10</v>
-      </c>
-      <c r="F44" s="80">
-        <v>10</v>
-      </c>
-      <c r="G44" s="82"/>
+      <c r="E44" s="3">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3">
+        <v>10</v>
+      </c>
+      <c r="G44" s="11"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="50" t="s">
+      <c r="B45" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="77">
+      <c r="C45" s="27">
         <v>2</v>
       </c>
-      <c r="D45" s="78" t="s">
+      <c r="D45" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="E45" s="152">
-        <v>10</v>
-      </c>
-      <c r="F45" s="85">
-        <v>10</v>
-      </c>
-      <c r="G45" s="84"/>
+      <c r="E45" s="29">
+        <v>10</v>
+      </c>
+      <c r="F45" s="29">
+        <v>10</v>
+      </c>
+      <c r="G45" s="22"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="51"/>
-      <c r="C46" s="76">
+      <c r="B46" s="63"/>
+      <c r="C46" s="24">
         <v>4</v>
       </c>
-      <c r="D46" s="78" t="s">
+      <c r="D46" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="E46" s="152">
-        <v>10</v>
-      </c>
-      <c r="F46" s="85">
-        <v>10</v>
-      </c>
-      <c r="G46" s="84"/>
+      <c r="E46" s="29">
+        <v>10</v>
+      </c>
+      <c r="F46" s="29">
+        <v>10</v>
+      </c>
+      <c r="G46" s="22"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="42" t="s">
+      <c r="B47" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="C47" s="75">
-        <v>5</v>
-      </c>
-      <c r="D47" s="64" t="s">
+      <c r="C47" s="23">
+        <v>5</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E47" s="135">
-        <v>5</v>
-      </c>
-      <c r="F47" s="80">
-        <v>5</v>
-      </c>
-      <c r="G47" s="82"/>
+      <c r="E47" s="3">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
+        <v>5</v>
+      </c>
+      <c r="G47" s="11"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="52"/>
-      <c r="C48" s="75">
+      <c r="B48" s="72"/>
+      <c r="C48" s="23">
         <v>6</v>
       </c>
-      <c r="D48" s="64" t="s">
+      <c r="D48" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E48" s="135">
-        <v>5</v>
-      </c>
-      <c r="F48" s="80">
-        <v>5</v>
-      </c>
-      <c r="G48" s="82"/>
+      <c r="E48" s="3">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
+        <v>5</v>
+      </c>
+      <c r="G48" s="11"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="52"/>
-      <c r="C49" s="63">
+      <c r="B49" s="72"/>
+      <c r="C49" s="2">
         <v>7</v>
       </c>
-      <c r="D49" s="64" t="s">
+      <c r="D49" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E49" s="135">
-        <v>5</v>
-      </c>
-      <c r="F49" s="80">
-        <v>5</v>
-      </c>
-      <c r="G49" s="82"/>
+      <c r="E49" s="3">
+        <v>5</v>
+      </c>
+      <c r="F49" s="3">
+        <v>5</v>
+      </c>
+      <c r="G49" s="11"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="52"/>
-      <c r="C50" s="63">
+      <c r="B50" s="72"/>
+      <c r="C50" s="2">
         <v>8</v>
       </c>
-      <c r="D50" s="64" t="s">
+      <c r="D50" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E50" s="135">
-        <v>5</v>
-      </c>
-      <c r="F50" s="80">
-        <v>5</v>
-      </c>
-      <c r="G50" s="82"/>
+      <c r="E50" s="3">
+        <v>5</v>
+      </c>
+      <c r="F50" s="3">
+        <v>5</v>
+      </c>
+      <c r="G50" s="11"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B51" s="52"/>
-      <c r="C51" s="134">
-        <v>10</v>
-      </c>
-      <c r="D51" s="135" t="s">
+      <c r="B51" s="72"/>
+      <c r="C51" s="2">
+        <v>10</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E51" s="135">
-        <v>5</v>
-      </c>
-      <c r="F51" s="80">
-        <v>5</v>
-      </c>
-      <c r="G51" s="82"/>
-    </row>
-    <row r="52" spans="2:7" s="133" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="52"/>
-      <c r="C52" s="134">
+      <c r="E51" s="3">
+        <v>5</v>
+      </c>
+      <c r="F51" s="3">
+        <v>5</v>
+      </c>
+      <c r="G51" s="11"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="72"/>
+      <c r="C52" s="2">
         <v>8</v>
       </c>
-      <c r="D52" s="135" t="s">
-        <v>140</v>
-      </c>
-      <c r="E52" s="135">
+      <c r="D52" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E52" s="3">
         <v>15</v>
       </c>
-      <c r="F52" s="135">
-        <v>0</v>
-      </c>
-      <c r="G52" s="140" t="s">
-        <v>142</v>
+      <c r="F52" s="37">
+        <v>0</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="53"/>
-      <c r="C53" s="134">
+      <c r="B53" s="73"/>
+      <c r="C53" s="2">
         <v>9</v>
       </c>
-      <c r="D53" s="135" t="s">
+      <c r="D53" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E53" s="135">
-        <v>10</v>
-      </c>
-      <c r="F53" s="80">
-        <v>10</v>
-      </c>
-      <c r="G53" s="82"/>
+      <c r="E53" s="3">
+        <v>10</v>
+      </c>
+      <c r="F53" s="3">
+        <v>10</v>
+      </c>
+      <c r="G53" s="11"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="73" t="s">
+      <c r="B54" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C54" s="79">
+      <c r="C54" s="30">
         <v>2</v>
       </c>
-      <c r="D54" s="65" t="s">
+      <c r="D54" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E54" s="136">
-        <v>5</v>
-      </c>
-      <c r="F54" s="81">
-        <v>5</v>
-      </c>
-      <c r="G54" s="83"/>
+      <c r="E54" s="4">
+        <v>5</v>
+      </c>
+      <c r="F54" s="4">
+        <v>5</v>
+      </c>
+      <c r="G54" s="15"/>
     </row>
     <row r="55" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="54" t="s">
+      <c r="B55" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="55"/>
-      <c r="D55" s="56"/>
-      <c r="E55" s="68">
+      <c r="C55" s="60"/>
+      <c r="D55" s="61"/>
+      <c r="E55" s="10">
         <f>SUM(E43:E54)</f>
         <v>100</v>
       </c>
-      <c r="F55" s="139">
+      <c r="F55" s="33">
         <f>SUM(F43:F54)</f>
         <v>85</v>
       </c>
-      <c r="G55" s="70"/>
-    </row>
-    <row r="57" spans="2:7" s="105" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="G55" s="35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B58" s="32" t="s">
+      <c r="B58" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="66"/>
+      <c r="D58" s="66"/>
+      <c r="E58" s="66"/>
+      <c r="F58" s="66"/>
+      <c r="G58" s="67"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="69"/>
+      <c r="D59" s="69"/>
+      <c r="E59" s="69"/>
+      <c r="F59" s="69"/>
+      <c r="G59" s="70"/>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B61" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="18">
+        <v>1</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E61" s="4">
+        <v>15</v>
+      </c>
+      <c r="F61" s="36">
+        <v>10</v>
+      </c>
+      <c r="G61" s="15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E62" s="3">
+        <v>10</v>
+      </c>
+      <c r="F62" s="3">
+        <v>10</v>
+      </c>
+      <c r="G62" s="11"/>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B63" s="71" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" s="27">
+        <v>2</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E63" s="29">
+        <v>10</v>
+      </c>
+      <c r="F63" s="29">
+        <v>10</v>
+      </c>
+      <c r="G63" s="22"/>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B64" s="63"/>
+      <c r="C64" s="24">
+        <v>4</v>
+      </c>
+      <c r="D64" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E64" s="29">
+        <v>10</v>
+      </c>
+      <c r="F64" s="29">
+        <v>10</v>
+      </c>
+      <c r="G64" s="22"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" s="23">
+        <v>5</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E65" s="3">
+        <v>5</v>
+      </c>
+      <c r="F65" s="37">
+        <v>0</v>
+      </c>
+      <c r="G65" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C58" s="45"/>
-      <c r="D58" s="45"/>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
-      <c r="G58" s="46"/>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B59" s="47" t="s">
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="72"/>
+      <c r="C66" s="23">
         <v>6</v>
       </c>
-      <c r="C59" s="48"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="49"/>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B60" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="C60" s="99" t="s">
-        <v>80</v>
-      </c>
-      <c r="D60" s="87" t="s">
-        <v>3</v>
-      </c>
-      <c r="E60" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="87" t="s">
-        <v>5</v>
-      </c>
-      <c r="G60" s="93" t="s">
+      <c r="D66" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5</v>
+      </c>
+      <c r="F66" s="37">
+        <v>0</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="72"/>
+      <c r="C67" s="2">
+        <v>7</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E67" s="3">
+        <v>5</v>
+      </c>
+      <c r="F67" s="37">
+        <v>0</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="72"/>
+      <c r="C68" s="2">
+        <v>8</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E68" s="3">
+        <v>5</v>
+      </c>
+      <c r="F68" s="37">
+        <v>0</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="72"/>
+      <c r="C69" s="2">
+        <v>10</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E69" s="3">
+        <v>5</v>
+      </c>
+      <c r="F69" s="3">
+        <v>5</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B70" s="72"/>
+      <c r="C70" s="2">
+        <v>8</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E70" s="3">
+        <v>15</v>
+      </c>
+      <c r="F70" s="37">
+        <v>0</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B71" s="73"/>
+      <c r="C71" s="2">
+        <v>9</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E71" s="3">
+        <v>10</v>
+      </c>
+      <c r="F71" s="37">
+        <v>0</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B72" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72" s="30">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B61" s="97" t="s">
-        <v>69</v>
-      </c>
-      <c r="C61" s="96">
-        <v>1</v>
-      </c>
-      <c r="D61" s="89" t="s">
-        <v>70</v>
-      </c>
-      <c r="E61" s="89">
-        <v>15</v>
-      </c>
-      <c r="F61" s="109">
-        <v>10</v>
-      </c>
-      <c r="G61" s="94" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B62" s="90" t="s">
-        <v>71</v>
-      </c>
-      <c r="C62" s="101" t="s">
-        <v>81</v>
-      </c>
-      <c r="D62" s="88" t="s">
-        <v>115</v>
-      </c>
-      <c r="E62" s="88">
-        <v>10</v>
-      </c>
-      <c r="F62" s="108">
-        <v>10</v>
-      </c>
-      <c r="G62" s="110"/>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B63" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="C63" s="103">
-        <v>2</v>
-      </c>
-      <c r="D63" s="104" t="s">
-        <v>79</v>
-      </c>
-      <c r="E63" s="104">
-        <v>10</v>
-      </c>
-      <c r="F63" s="112">
-        <v>10</v>
-      </c>
-      <c r="G63" s="100"/>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B64" s="51"/>
-      <c r="C64" s="102">
+      <c r="D72" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E72" s="4">
+        <v>5</v>
+      </c>
+      <c r="F72" s="4">
+        <v>5</v>
+      </c>
+      <c r="G72" s="22"/>
+    </row>
+    <row r="73" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="D64" s="104" t="s">
-        <v>116</v>
-      </c>
-      <c r="E64" s="104">
-        <v>10</v>
-      </c>
-      <c r="F64" s="107">
-        <v>8</v>
-      </c>
-      <c r="G64" s="100" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B65" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C65" s="101">
-        <v>5</v>
-      </c>
-      <c r="D65" s="88" t="s">
-        <v>117</v>
-      </c>
-      <c r="E65" s="88">
-        <v>5</v>
-      </c>
-      <c r="F65" s="108">
-        <v>0</v>
-      </c>
-      <c r="G65" s="110" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="52"/>
-      <c r="C66" s="101">
-        <v>6</v>
-      </c>
-      <c r="D66" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="E66" s="88">
-        <v>5</v>
-      </c>
-      <c r="F66" s="106">
-        <v>0</v>
-      </c>
-      <c r="G66" s="110" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B67" s="52"/>
-      <c r="C67" s="87">
-        <v>7</v>
-      </c>
-      <c r="D67" s="88" t="s">
-        <v>119</v>
-      </c>
-      <c r="E67" s="88">
-        <v>5</v>
-      </c>
-      <c r="F67" s="106">
-        <v>0</v>
-      </c>
-      <c r="G67" s="110" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B68" s="52"/>
-      <c r="C68" s="87">
-        <v>8</v>
-      </c>
-      <c r="D68" s="88" t="s">
-        <v>120</v>
-      </c>
-      <c r="E68" s="88">
-        <v>5</v>
-      </c>
-      <c r="F68" s="106">
-        <v>0</v>
-      </c>
-      <c r="G68" s="110" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B69" s="52"/>
-      <c r="C69" s="134">
-        <v>10</v>
-      </c>
-      <c r="D69" s="135" t="s">
-        <v>122</v>
-      </c>
-      <c r="E69" s="135">
-        <v>5</v>
-      </c>
-      <c r="F69" s="106">
-        <v>0</v>
-      </c>
-      <c r="G69" s="110" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="70" spans="2:7" s="133" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="52"/>
-      <c r="C70" s="134">
-        <v>8</v>
-      </c>
-      <c r="D70" s="135" t="s">
-        <v>140</v>
-      </c>
-      <c r="E70" s="135">
-        <v>15</v>
-      </c>
-      <c r="F70" s="135">
-        <v>0</v>
-      </c>
-      <c r="G70" s="140"/>
-    </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B71" s="53"/>
-      <c r="C71" s="134">
-        <v>9</v>
-      </c>
-      <c r="D71" s="135" t="s">
-        <v>121</v>
-      </c>
-      <c r="E71" s="135">
-        <v>10</v>
-      </c>
-      <c r="F71" s="106">
-        <v>0</v>
-      </c>
-      <c r="G71" s="110" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B72" s="98" t="s">
-        <v>73</v>
-      </c>
-      <c r="C72" s="153">
-        <v>2</v>
-      </c>
-      <c r="D72" s="136" t="s">
-        <v>74</v>
-      </c>
-      <c r="E72" s="136">
-        <v>5</v>
-      </c>
-      <c r="F72" s="109">
-        <v>0</v>
-      </c>
-      <c r="G72" s="111" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="73" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="C73" s="55"/>
-      <c r="D73" s="56"/>
-      <c r="E73" s="92">
+      <c r="C73" s="60"/>
+      <c r="D73" s="61"/>
+      <c r="E73" s="10">
         <f>SUM(E61:E72)</f>
         <v>100</v>
       </c>
-      <c r="F73" s="92">
+      <c r="F73" s="33">
         <f>SUM(F61:F72)</f>
-        <v>38</v>
-      </c>
-      <c r="G73" s="95"/>
-    </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B74" s="86"/>
-      <c r="C74" s="86"/>
-      <c r="D74" s="86"/>
-      <c r="E74" s="86"/>
-      <c r="F74" s="86"/>
-      <c r="G74" s="86"/>
+        <v>50</v>
+      </c>
+      <c r="G73" s="34" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="76" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="77" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B77" s="32" t="s">
+      <c r="B77" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C77" s="66"/>
+      <c r="D77" s="66"/>
+      <c r="E77" s="66"/>
+      <c r="F77" s="66"/>
+      <c r="G77" s="67"/>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="69"/>
+      <c r="D78" s="69"/>
+      <c r="E78" s="69"/>
+      <c r="F78" s="69"/>
+      <c r="G78" s="70"/>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G79" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C80" s="18">
+        <v>1</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E80" s="4">
+        <v>15</v>
+      </c>
+      <c r="F80" s="4">
+        <v>15</v>
+      </c>
+      <c r="G80" s="15"/>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B81" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C81" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E81" s="3">
+        <v>10</v>
+      </c>
+      <c r="F81" s="37">
+        <v>0</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="71" t="s">
+        <v>78</v>
+      </c>
+      <c r="C82" s="27">
+        <v>2</v>
+      </c>
+      <c r="D82" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E82" s="29">
+        <v>10</v>
+      </c>
+      <c r="F82" s="29">
+        <v>10</v>
+      </c>
+      <c r="G82" s="22"/>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B83" s="63"/>
+      <c r="C83" s="24">
+        <v>4</v>
+      </c>
+      <c r="D83" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E83" s="29">
+        <v>10</v>
+      </c>
+      <c r="F83" s="29">
+        <v>10</v>
+      </c>
+      <c r="G83" s="22"/>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B84" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C84" s="23">
+        <v>5</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E84" s="3">
+        <v>5</v>
+      </c>
+      <c r="F84" s="3">
+        <v>5</v>
+      </c>
+      <c r="G84" s="11"/>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B85" s="72"/>
+      <c r="C85" s="23">
+        <v>6</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E85" s="3">
+        <v>5</v>
+      </c>
+      <c r="F85" s="3">
+        <v>5</v>
+      </c>
+      <c r="G85" s="11"/>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B86" s="72"/>
+      <c r="C86" s="2">
+        <v>7</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E86" s="3">
+        <v>5</v>
+      </c>
+      <c r="F86" s="3">
+        <v>5</v>
+      </c>
+      <c r="G86" s="11"/>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B87" s="72"/>
+      <c r="C87" s="2">
+        <v>8</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E87" s="3">
+        <v>5</v>
+      </c>
+      <c r="F87" s="3">
+        <v>5</v>
+      </c>
+      <c r="G87" s="11"/>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B88" s="72"/>
+      <c r="C88" s="2">
+        <v>10</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E88" s="3">
+        <v>5</v>
+      </c>
+      <c r="F88" s="3">
+        <v>5</v>
+      </c>
+      <c r="G88" s="11"/>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B89" s="72"/>
+      <c r="C89" s="2">
+        <v>8</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C77" s="45"/>
-      <c r="D77" s="45"/>
-      <c r="E77" s="45"/>
-      <c r="F77" s="45"/>
-      <c r="G77" s="46"/>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B78" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="48"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="49"/>
-    </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B79" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="C79" s="127" t="s">
-        <v>80</v>
-      </c>
-      <c r="D79" s="114" t="s">
-        <v>3</v>
-      </c>
-      <c r="E79" s="114" t="s">
-        <v>1</v>
-      </c>
-      <c r="F79" s="114" t="s">
-        <v>5</v>
-      </c>
-      <c r="G79" s="121" t="s">
+      <c r="E89" s="3">
+        <v>15</v>
+      </c>
+      <c r="F89" s="3">
+        <v>15</v>
+      </c>
+      <c r="G89" s="11"/>
+    </row>
+    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B90" s="73"/>
+      <c r="C90" s="2">
+        <v>9</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E90" s="3">
+        <v>10</v>
+      </c>
+      <c r="F90" s="37">
+        <v>0</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B91" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C91" s="30">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B80" s="125" t="s">
-        <v>69</v>
-      </c>
-      <c r="C80" s="124">
-        <v>1</v>
-      </c>
-      <c r="D80" s="116" t="s">
-        <v>70</v>
-      </c>
-      <c r="E80" s="116">
-        <v>15</v>
-      </c>
-      <c r="F80" s="116">
-        <v>15</v>
-      </c>
-      <c r="G80" s="122"/>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B81" s="117" t="s">
-        <v>71</v>
-      </c>
-      <c r="C81" s="129" t="s">
-        <v>81</v>
-      </c>
-      <c r="D81" s="115" t="s">
-        <v>115</v>
-      </c>
-      <c r="E81" s="115">
-        <v>10</v>
-      </c>
-      <c r="F81" s="115">
-        <v>0</v>
-      </c>
-      <c r="G81" s="120" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="C82" s="131">
-        <v>2</v>
-      </c>
-      <c r="D82" s="132" t="s">
-        <v>79</v>
-      </c>
-      <c r="E82" s="132">
-        <v>10</v>
-      </c>
-      <c r="F82" s="132">
-        <v>10</v>
-      </c>
-      <c r="G82" s="128"/>
-    </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B83" s="51"/>
-      <c r="C83" s="130">
+      <c r="D91" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E91" s="4">
+        <v>5</v>
+      </c>
+      <c r="F91" s="4">
+        <v>5</v>
+      </c>
+      <c r="G91" s="15"/>
+    </row>
+    <row r="92" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B92" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="D83" s="132" t="s">
-        <v>116</v>
-      </c>
-      <c r="E83" s="132">
-        <v>10</v>
-      </c>
-      <c r="F83" s="132">
-        <v>10</v>
-      </c>
-      <c r="G83" s="128"/>
-    </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B84" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C84" s="129">
-        <v>5</v>
-      </c>
-      <c r="D84" s="115" t="s">
-        <v>117</v>
-      </c>
-      <c r="E84" s="115">
-        <v>5</v>
-      </c>
-      <c r="F84" s="115">
-        <v>5</v>
-      </c>
-      <c r="G84" s="120"/>
-    </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B85" s="52"/>
-      <c r="C85" s="129">
-        <v>6</v>
-      </c>
-      <c r="D85" s="115" t="s">
-        <v>118</v>
-      </c>
-      <c r="E85" s="115">
-        <v>5</v>
-      </c>
-      <c r="F85" s="115">
-        <v>5</v>
-      </c>
-      <c r="G85" s="120"/>
-    </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B86" s="52"/>
-      <c r="C86" s="114">
-        <v>7</v>
-      </c>
-      <c r="D86" s="115" t="s">
-        <v>119</v>
-      </c>
-      <c r="E86" s="115">
-        <v>5</v>
-      </c>
-      <c r="F86" s="115">
-        <v>5</v>
-      </c>
-      <c r="G86" s="120"/>
-    </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B87" s="52"/>
-      <c r="C87" s="114">
-        <v>8</v>
-      </c>
-      <c r="D87" s="115" t="s">
-        <v>120</v>
-      </c>
-      <c r="E87" s="115">
-        <v>5</v>
-      </c>
-      <c r="F87" s="115">
-        <v>5</v>
-      </c>
-      <c r="G87" s="120"/>
-    </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B88" s="52"/>
-      <c r="C88" s="134">
-        <v>10</v>
-      </c>
-      <c r="D88" s="135" t="s">
-        <v>122</v>
-      </c>
-      <c r="E88" s="135">
-        <v>5</v>
-      </c>
-      <c r="F88" s="115">
-        <v>5</v>
-      </c>
-      <c r="G88" s="120"/>
-    </row>
-    <row r="89" spans="2:7" s="133" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="52"/>
-      <c r="C89" s="134">
-        <v>8</v>
-      </c>
-      <c r="D89" s="135" t="s">
-        <v>140</v>
-      </c>
-      <c r="E89" s="135">
-        <v>15</v>
-      </c>
-      <c r="F89" s="135">
-        <v>15</v>
-      </c>
-      <c r="G89" s="140"/>
-    </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B90" s="53"/>
-      <c r="C90" s="134">
-        <v>9</v>
-      </c>
-      <c r="D90" s="135" t="s">
-        <v>121</v>
-      </c>
-      <c r="E90" s="135">
-        <v>10</v>
-      </c>
-      <c r="F90" s="115">
-        <v>0</v>
-      </c>
-      <c r="G90" s="120" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B91" s="126" t="s">
-        <v>73</v>
-      </c>
-      <c r="C91" s="153">
-        <v>2</v>
-      </c>
-      <c r="D91" s="136" t="s">
-        <v>74</v>
-      </c>
-      <c r="E91" s="136">
-        <v>5</v>
-      </c>
-      <c r="F91" s="116">
-        <v>5</v>
-      </c>
-      <c r="G91" s="122"/>
-    </row>
-    <row r="92" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="C92" s="55"/>
-      <c r="D92" s="56"/>
-      <c r="E92" s="119">
+      <c r="C92" s="60"/>
+      <c r="D92" s="61"/>
+      <c r="E92" s="10">
         <f>SUM(E80:E91)</f>
         <v>100</v>
       </c>
-      <c r="F92" s="119">
+      <c r="F92" s="33">
         <f>SUM(F80:F91)</f>
         <v>80</v>
       </c>
-      <c r="G92" s="123"/>
+      <c r="G92" s="35" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="95" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B96" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="C96" s="45"/>
-      <c r="D96" s="45"/>
-      <c r="E96" s="45"/>
-      <c r="F96" s="45"/>
-      <c r="G96" s="46"/>
+      <c r="B96" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C96" s="66"/>
+      <c r="D96" s="66"/>
+      <c r="E96" s="66"/>
+      <c r="F96" s="66"/>
+      <c r="G96" s="67"/>
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B97" s="47" t="s">
+      <c r="B97" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C97" s="48"/>
-      <c r="D97" s="48"/>
-      <c r="E97" s="48"/>
-      <c r="F97" s="48"/>
-      <c r="G97" s="49"/>
+      <c r="C97" s="69"/>
+      <c r="D97" s="69"/>
+      <c r="E97" s="69"/>
+      <c r="F97" s="69"/>
+      <c r="G97" s="70"/>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B98" s="138" t="s">
-        <v>0</v>
-      </c>
-      <c r="C98" s="147" t="s">
+      <c r="B98" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C98" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D98" s="134" t="s">
+      <c r="D98" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E98" s="134" t="s">
+      <c r="E98" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F98" s="134" t="s">
-        <v>5</v>
-      </c>
-      <c r="G98" s="141" t="s">
+      <c r="F98" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G98" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B99" s="145" t="s">
+      <c r="B99" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C99" s="144">
+      <c r="C99" s="18">
         <v>1</v>
       </c>
-      <c r="D99" s="136" t="s">
+      <c r="D99" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E99" s="136">
+      <c r="E99" s="4">
         <v>15</v>
       </c>
-      <c r="F99" s="136"/>
-      <c r="G99" s="142"/>
+      <c r="F99" s="4">
+        <v>15</v>
+      </c>
+      <c r="G99" s="15"/>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B100" s="137" t="s">
+      <c r="B100" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C100" s="149" t="s">
+      <c r="C100" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="D100" s="135" t="s">
+      <c r="D100" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E100" s="135">
-        <v>10</v>
-      </c>
-      <c r="F100" s="135"/>
-      <c r="G100" s="140"/>
+      <c r="E100" s="3">
+        <v>10</v>
+      </c>
+      <c r="F100" s="3">
+        <v>10</v>
+      </c>
+      <c r="G100" s="11"/>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B101" s="50" t="s">
+      <c r="B101" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="C101" s="151">
+      <c r="C101" s="27">
         <v>2</v>
       </c>
-      <c r="D101" s="152" t="s">
+      <c r="D101" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="E101" s="152">
-        <v>10</v>
-      </c>
-      <c r="F101" s="152"/>
-      <c r="G101" s="148"/>
+      <c r="E101" s="29">
+        <v>10</v>
+      </c>
+      <c r="F101" s="29">
+        <v>10</v>
+      </c>
+      <c r="G101" s="22"/>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B102" s="51"/>
-      <c r="C102" s="150">
+      <c r="B102" s="63"/>
+      <c r="C102" s="24">
         <v>4</v>
       </c>
-      <c r="D102" s="152" t="s">
+      <c r="D102" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="E102" s="152">
-        <v>10</v>
-      </c>
-      <c r="F102" s="152"/>
-      <c r="G102" s="148"/>
+      <c r="E102" s="29">
+        <v>10</v>
+      </c>
+      <c r="F102" s="29">
+        <v>10</v>
+      </c>
+      <c r="G102" s="22"/>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B103" s="42" t="s">
+      <c r="B103" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="C103" s="149">
-        <v>5</v>
-      </c>
-      <c r="D103" s="135" t="s">
+      <c r="C103" s="23">
+        <v>5</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E103" s="135">
-        <v>5</v>
-      </c>
-      <c r="F103" s="135"/>
-      <c r="G103" s="140"/>
+      <c r="E103" s="3">
+        <v>5</v>
+      </c>
+      <c r="F103" s="3">
+        <v>5</v>
+      </c>
+      <c r="G103" s="11"/>
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B104" s="52"/>
-      <c r="C104" s="149">
+      <c r="B104" s="72"/>
+      <c r="C104" s="23">
         <v>6</v>
       </c>
-      <c r="D104" s="135" t="s">
+      <c r="D104" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E104" s="135">
-        <v>5</v>
-      </c>
-      <c r="F104" s="135"/>
-      <c r="G104" s="140"/>
+      <c r="E104" s="3">
+        <v>5</v>
+      </c>
+      <c r="F104" s="3">
+        <v>5</v>
+      </c>
+      <c r="G104" s="11"/>
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B105" s="52"/>
-      <c r="C105" s="134">
+      <c r="B105" s="72"/>
+      <c r="C105" s="2">
         <v>7</v>
       </c>
-      <c r="D105" s="135" t="s">
+      <c r="D105" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E105" s="135">
-        <v>5</v>
-      </c>
-      <c r="F105" s="135"/>
-      <c r="G105" s="140"/>
+      <c r="E105" s="3">
+        <v>5</v>
+      </c>
+      <c r="F105" s="37">
+        <v>0</v>
+      </c>
+      <c r="G105" s="11" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B106" s="52"/>
-      <c r="C106" s="134">
+      <c r="B106" s="72"/>
+      <c r="C106" s="2">
         <v>8</v>
       </c>
-      <c r="D106" s="135" t="s">
+      <c r="D106" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E106" s="135">
-        <v>5</v>
-      </c>
-      <c r="F106" s="135"/>
-      <c r="G106" s="140"/>
+      <c r="E106" s="3">
+        <v>5</v>
+      </c>
+      <c r="F106" s="3">
+        <v>5</v>
+      </c>
+      <c r="G106" s="11"/>
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B107" s="52"/>
-      <c r="C107" s="134">
-        <v>10</v>
-      </c>
-      <c r="D107" s="135" t="s">
+      <c r="B107" s="72"/>
+      <c r="C107" s="2">
+        <v>10</v>
+      </c>
+      <c r="D107" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E107" s="135">
-        <v>5</v>
-      </c>
-      <c r="F107" s="135"/>
-      <c r="G107" s="140"/>
+      <c r="E107" s="3">
+        <v>5</v>
+      </c>
+      <c r="F107" s="3">
+        <v>5</v>
+      </c>
+      <c r="G107" s="11"/>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B108" s="52"/>
-      <c r="C108" s="134">
+      <c r="B108" s="72"/>
+      <c r="C108" s="2">
         <v>8</v>
       </c>
-      <c r="D108" s="135" t="s">
-        <v>140</v>
-      </c>
-      <c r="E108" s="135">
+      <c r="D108" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E108" s="3">
         <v>15</v>
       </c>
-      <c r="F108" s="135"/>
-      <c r="G108" s="140"/>
+      <c r="F108" s="3">
+        <v>15</v>
+      </c>
+      <c r="G108" s="11"/>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B109" s="53"/>
-      <c r="C109" s="134">
+      <c r="B109" s="73"/>
+      <c r="C109" s="2">
         <v>9</v>
       </c>
-      <c r="D109" s="135" t="s">
+      <c r="D109" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E109" s="135">
-        <v>10</v>
-      </c>
-      <c r="F109" s="135"/>
-      <c r="G109" s="140"/>
+      <c r="E109" s="3">
+        <v>10</v>
+      </c>
+      <c r="F109" s="37">
+        <v>0</v>
+      </c>
+      <c r="G109" s="11" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B110" s="146" t="s">
+      <c r="B110" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C110" s="153">
+      <c r="C110" s="30">
         <v>2</v>
       </c>
-      <c r="D110" s="136" t="s">
+      <c r="D110" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E110" s="136">
-        <v>5</v>
-      </c>
-      <c r="F110" s="136"/>
-      <c r="G110" s="142"/>
+      <c r="E110" s="4">
+        <v>5</v>
+      </c>
+      <c r="F110" s="4">
+        <v>5</v>
+      </c>
+      <c r="G110" s="15"/>
     </row>
     <row r="111" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B111" s="54" t="s">
+      <c r="B111" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C111" s="55"/>
-      <c r="D111" s="56"/>
-      <c r="E111" s="139">
+      <c r="C111" s="60"/>
+      <c r="D111" s="61"/>
+      <c r="E111" s="10">
         <f>SUM(E99:E110)</f>
         <v>100</v>
       </c>
-      <c r="F111" s="139">
+      <c r="F111" s="33">
         <f>SUM(F99:F110)</f>
-        <v>0</v>
-      </c>
-      <c r="G111" s="143"/>
+        <v>85</v>
+      </c>
+      <c r="G111" s="35" t="s">
+        <v>145</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B16"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B47:B53"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B59:G59"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B65:B71"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="B78:G78"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="B84:B90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B35"/>
     <mergeCell ref="B96:G96"/>
     <mergeCell ref="B97:G97"/>
     <mergeCell ref="B101:B102"/>
     <mergeCell ref="B103:B109"/>
     <mergeCell ref="B111:D111"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B35"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="B78:G78"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B84:B90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B59:G59"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B65:B71"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B41:G41"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B47:B53"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B16"/>
-    <mergeCell ref="B18:D18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5066,7 +7463,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2BB600F-9175-4C95-9A78-5CEDB543EB79}">
-  <dimension ref="B2:G17"/>
+  <dimension ref="B2:G108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -5075,30 +7472,30 @@
     <col min="4" max="4" width="54" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="1"/>
     <col min="6" max="6" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="67" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="35"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="41"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -5137,7 +7534,7 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="64" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="23" t="s">
@@ -5153,7 +7550,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="59"/>
+      <c r="B8" s="65"/>
       <c r="C8" s="23" t="s">
         <v>89</v>
       </c>
@@ -5167,7 +7564,7 @@
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="53" t="s">
         <v>78</v>
       </c>
       <c r="C9" s="27">
@@ -5183,7 +7580,7 @@
       <c r="G9" s="22"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="44"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="24">
         <v>5</v>
       </c>
@@ -5197,7 +7594,7 @@
       <c r="G10" s="22"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="55" t="s">
         <v>75</v>
       </c>
       <c r="C11" s="23">
@@ -5213,7 +7610,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="42"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -5227,7 +7624,7 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="42"/>
+      <c r="B13" s="55"/>
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -5241,7 +7638,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
+      <c r="B14" s="55"/>
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -5255,7 +7652,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="42"/>
+      <c r="B15" s="55"/>
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -5285,23 +7682,1337 @@
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
       <c r="E17" s="10">
         <f>SUM(E6:E16)</f>
         <v>100</v>
       </c>
       <c r="F17" s="10">
-        <f>SUM(F6:F9)</f>
+        <f>SUM(F6:F16)</f>
         <v>0</v>
       </c>
       <c r="G17" s="16"/>
     </row>
+    <row r="20" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="47"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="52"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="18">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="4">
+        <v>15</v>
+      </c>
+      <c r="F24" s="4">
+        <v>15</v>
+      </c>
+      <c r="G24" s="15"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="3">
+        <v>5</v>
+      </c>
+      <c r="F25" s="3">
+        <v>5</v>
+      </c>
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="65"/>
+      <c r="C26" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5</v>
+      </c>
+      <c r="F26" s="37">
+        <v>0</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="27">
+        <v>2</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="29">
+        <v>10</v>
+      </c>
+      <c r="F27" s="29">
+        <v>10</v>
+      </c>
+      <c r="G27" s="22"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="54"/>
+      <c r="C28" s="24">
+        <v>5</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="29">
+        <v>10</v>
+      </c>
+      <c r="F28" s="38">
+        <v>5</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="23">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="3">
+        <v>6</v>
+      </c>
+      <c r="F29" s="37">
+        <v>0</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="55"/>
+      <c r="C30" s="2">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="3">
+        <v>6</v>
+      </c>
+      <c r="F30" s="37">
+        <v>0</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="55"/>
+      <c r="C31" s="2">
+        <v>8</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="3">
+        <v>6</v>
+      </c>
+      <c r="F31" s="37">
+        <v>0</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="55"/>
+      <c r="C32" s="2">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="3">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3">
+        <v>16</v>
+      </c>
+      <c r="G32" s="11"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="55"/>
+      <c r="C33" s="2">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="3">
+        <v>16</v>
+      </c>
+      <c r="F33" s="37">
+        <v>0</v>
+      </c>
+      <c r="G33" s="11"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="30">
+        <v>2</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="4">
+        <v>5</v>
+      </c>
+      <c r="F34" s="4">
+        <v>5</v>
+      </c>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="57"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="10">
+        <f>SUM(E24:E34)</f>
+        <v>100</v>
+      </c>
+      <c r="F35" s="33">
+        <f>SUM(F24:F34)</f>
+        <v>56</v>
+      </c>
+      <c r="G35" s="34" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="C38" s="47"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="49"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="51"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="52"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="18">
+        <v>1</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E41" s="4">
+        <v>15</v>
+      </c>
+      <c r="F41" s="4">
+        <v>15</v>
+      </c>
+      <c r="G41" s="15"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5</v>
+      </c>
+      <c r="F42" s="3">
+        <v>5</v>
+      </c>
+      <c r="G42" s="11"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="65"/>
+      <c r="C43" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3">
+        <v>5</v>
+      </c>
+      <c r="G43" s="11"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="27">
+        <v>2</v>
+      </c>
+      <c r="D44" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="29">
+        <v>10</v>
+      </c>
+      <c r="F44" s="29">
+        <v>10</v>
+      </c>
+      <c r="G44" s="22"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="54"/>
+      <c r="C45" s="24">
+        <v>5</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E45" s="29">
+        <v>10</v>
+      </c>
+      <c r="F45" s="38">
+        <v>0</v>
+      </c>
+      <c r="G45" s="22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C46" s="23">
+        <v>6</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6</v>
+      </c>
+      <c r="F46" s="37">
+        <v>0</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="55"/>
+      <c r="C47" s="2">
+        <v>7</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6</v>
+      </c>
+      <c r="F47" s="3">
+        <v>6</v>
+      </c>
+      <c r="G47" s="11"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="55"/>
+      <c r="C48" s="2">
+        <v>8</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3">
+        <v>6</v>
+      </c>
+      <c r="G48" s="11"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="55"/>
+      <c r="C49" s="2">
+        <v>9</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E49" s="3">
+        <v>16</v>
+      </c>
+      <c r="F49" s="3">
+        <v>16</v>
+      </c>
+      <c r="G49" s="11"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="55"/>
+      <c r="C50" s="2">
+        <v>10</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E50" s="3">
+        <v>16</v>
+      </c>
+      <c r="F50" s="3">
+        <v>16</v>
+      </c>
+      <c r="G50" s="11"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="30">
+        <v>2</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" s="4">
+        <v>5</v>
+      </c>
+      <c r="F51" s="4">
+        <v>5</v>
+      </c>
+      <c r="G51" s="15"/>
+    </row>
+    <row r="52" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="57"/>
+      <c r="D52" s="58"/>
+      <c r="E52" s="10">
+        <f>SUM(E41:E51)</f>
+        <v>100</v>
+      </c>
+      <c r="F52" s="33">
+        <f>SUM(F41:F51)</f>
+        <v>84</v>
+      </c>
+      <c r="G52" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="C56" s="47"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="49"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="51"/>
+      <c r="D57" s="51"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="51"/>
+      <c r="G57" s="52"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="18">
+        <v>1</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" s="4">
+        <v>15</v>
+      </c>
+      <c r="F59" s="4">
+        <v>15</v>
+      </c>
+      <c r="G59" s="15"/>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3">
+        <v>5</v>
+      </c>
+      <c r="G60" s="11"/>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B61" s="65"/>
+      <c r="C61" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5</v>
+      </c>
+      <c r="F61" s="3">
+        <v>5</v>
+      </c>
+      <c r="G61" s="11"/>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" s="27">
+        <v>2</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E62" s="29">
+        <v>10</v>
+      </c>
+      <c r="F62" s="29">
+        <v>10</v>
+      </c>
+      <c r="G62" s="22"/>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B63" s="54"/>
+      <c r="C63" s="24">
+        <v>5</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E63" s="29">
+        <v>10</v>
+      </c>
+      <c r="F63" s="29">
+        <v>10</v>
+      </c>
+      <c r="G63" s="22"/>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B64" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C64" s="23">
+        <v>6</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E64" s="3">
+        <v>6</v>
+      </c>
+      <c r="F64" s="37">
+        <v>0</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="55"/>
+      <c r="C65" s="2">
+        <v>7</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E65" s="3">
+        <v>6</v>
+      </c>
+      <c r="F65" s="37">
+        <v>0</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="55"/>
+      <c r="C66" s="2">
+        <v>8</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6</v>
+      </c>
+      <c r="F66" s="37">
+        <v>0</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="55"/>
+      <c r="C67" s="2">
+        <v>9</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E67" s="3">
+        <v>16</v>
+      </c>
+      <c r="F67" s="37">
+        <v>0</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="55"/>
+      <c r="C68" s="2">
+        <v>10</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E68" s="3">
+        <v>16</v>
+      </c>
+      <c r="F68" s="37">
+        <v>0</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="30">
+        <v>2</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E69" s="4">
+        <v>5</v>
+      </c>
+      <c r="F69" s="36">
+        <v>0</v>
+      </c>
+      <c r="G69" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="57"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="10">
+        <f>SUM(E59:E69)</f>
+        <v>100</v>
+      </c>
+      <c r="F70" s="42">
+        <f>SUM(F59:F69)</f>
+        <v>45</v>
+      </c>
+      <c r="G70" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F71" s="40" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B75" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C75" s="47"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="49"/>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="51"/>
+      <c r="D76" s="51"/>
+      <c r="E76" s="51"/>
+      <c r="F76" s="51"/>
+      <c r="G76" s="52"/>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G77" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C78" s="18">
+        <v>1</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E78" s="4">
+        <v>15</v>
+      </c>
+      <c r="F78" s="4">
+        <v>15</v>
+      </c>
+      <c r="G78" s="15"/>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C79" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E79" s="3">
+        <v>5</v>
+      </c>
+      <c r="F79" s="37">
+        <v>0</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="65"/>
+      <c r="C80" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E80" s="3">
+        <v>5</v>
+      </c>
+      <c r="F80" s="37">
+        <v>0</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B81" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C81" s="27">
+        <v>2</v>
+      </c>
+      <c r="D81" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E81" s="29">
+        <v>10</v>
+      </c>
+      <c r="F81" s="29">
+        <v>10</v>
+      </c>
+      <c r="G81" s="22"/>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="54"/>
+      <c r="C82" s="24">
+        <v>5</v>
+      </c>
+      <c r="D82" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E82" s="29">
+        <v>10</v>
+      </c>
+      <c r="F82" s="38">
+        <v>0</v>
+      </c>
+      <c r="G82" s="22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B83" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C83" s="23">
+        <v>6</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E83" s="3">
+        <v>6</v>
+      </c>
+      <c r="F83" s="37">
+        <v>0</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B84" s="55"/>
+      <c r="C84" s="2">
+        <v>7</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E84" s="3">
+        <v>6</v>
+      </c>
+      <c r="F84" s="37">
+        <v>0</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B85" s="55"/>
+      <c r="C85" s="2">
+        <v>8</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E85" s="3">
+        <v>6</v>
+      </c>
+      <c r="F85" s="41">
+        <v>6</v>
+      </c>
+      <c r="G85" s="11"/>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B86" s="55"/>
+      <c r="C86" s="2">
+        <v>9</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E86" s="3">
+        <v>16</v>
+      </c>
+      <c r="F86" s="37">
+        <v>0</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B87" s="55"/>
+      <c r="C87" s="2">
+        <v>10</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E87" s="3">
+        <v>16</v>
+      </c>
+      <c r="F87" s="37">
+        <v>0</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B88" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C88" s="30">
+        <v>2</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E88" s="4">
+        <v>5</v>
+      </c>
+      <c r="F88" s="38">
+        <v>0</v>
+      </c>
+      <c r="G88" s="22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" s="57"/>
+      <c r="D89" s="58"/>
+      <c r="E89" s="10">
+        <f>SUM(E78:E88)</f>
+        <v>100</v>
+      </c>
+      <c r="F89" s="42">
+        <f>SUM(F78:F88)</f>
+        <v>31</v>
+      </c>
+      <c r="G89" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B94" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="C94" s="47"/>
+      <c r="D94" s="48"/>
+      <c r="E94" s="48"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="49"/>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B95" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="51"/>
+      <c r="D95" s="51"/>
+      <c r="E95" s="51"/>
+      <c r="F95" s="51"/>
+      <c r="G95" s="52"/>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B96" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C96" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B97" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C97" s="18">
+        <v>1</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E97" s="4">
+        <v>15</v>
+      </c>
+      <c r="F97" s="4">
+        <v>15</v>
+      </c>
+      <c r="G97" s="15"/>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B98" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C98" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E98" s="3">
+        <v>5</v>
+      </c>
+      <c r="F98" s="41">
+        <v>5</v>
+      </c>
+      <c r="G98" s="11"/>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B99" s="65"/>
+      <c r="C99" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E99" s="3">
+        <v>5</v>
+      </c>
+      <c r="F99" s="41">
+        <v>5</v>
+      </c>
+      <c r="G99" s="11"/>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B100" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C100" s="27">
+        <v>2</v>
+      </c>
+      <c r="D100" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E100" s="29">
+        <v>10</v>
+      </c>
+      <c r="F100" s="43">
+        <v>0</v>
+      </c>
+      <c r="G100" s="22" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B101" s="54"/>
+      <c r="C101" s="24">
+        <v>5</v>
+      </c>
+      <c r="D101" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E101" s="29">
+        <v>10</v>
+      </c>
+      <c r="F101" s="43">
+        <v>10</v>
+      </c>
+      <c r="G101" s="22"/>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B102" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C102" s="23">
+        <v>6</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E102" s="3">
+        <v>6</v>
+      </c>
+      <c r="F102" s="37">
+        <v>0</v>
+      </c>
+      <c r="G102" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B103" s="55"/>
+      <c r="C103" s="2">
+        <v>7</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E103" s="3">
+        <v>6</v>
+      </c>
+      <c r="F103" s="37">
+        <v>0</v>
+      </c>
+      <c r="G103" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B104" s="55"/>
+      <c r="C104" s="2">
+        <v>8</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E104" s="3">
+        <v>6</v>
+      </c>
+      <c r="F104" s="37">
+        <v>0</v>
+      </c>
+      <c r="G104" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B105" s="55"/>
+      <c r="C105" s="2">
+        <v>9</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E105" s="3">
+        <v>16</v>
+      </c>
+      <c r="F105" s="37">
+        <v>0</v>
+      </c>
+      <c r="G105" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B106" s="55"/>
+      <c r="C106" s="2">
+        <v>10</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E106" s="3">
+        <v>16</v>
+      </c>
+      <c r="F106" s="41">
+        <v>16</v>
+      </c>
+      <c r="G106" s="11"/>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B107" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C107" s="30">
+        <v>2</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E107" s="4">
+        <v>5</v>
+      </c>
+      <c r="F107" s="38">
+        <v>0</v>
+      </c>
+      <c r="G107" s="22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B108" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="57"/>
+      <c r="D108" s="58"/>
+      <c r="E108" s="10">
+        <f>SUM(E97:E107)</f>
+        <v>100</v>
+      </c>
+      <c r="F108" s="33">
+        <f>SUM(F97:F107)</f>
+        <v>51</v>
+      </c>
+      <c r="G108" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="36">
+    <mergeCell ref="B95:G95"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="B102:B106"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="B83:B87"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B94:G94"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B64:B68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B46:B50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B33"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B17:D17"/>
@@ -5316,7 +9027,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2730F805-5A91-4E33-9A4F-593CF296DB62}">
-  <dimension ref="B2:G17"/>
+  <dimension ref="B2:G107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -5325,30 +9036,30 @@
     <col min="4" max="4" width="67.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="1"/>
     <col min="6" max="6" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="45.140625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="35"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="41"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -5387,7 +9098,7 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="64" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="23" t="s">
@@ -5403,7 +9114,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="59"/>
+      <c r="B8" s="65"/>
       <c r="C8" s="23" t="s">
         <v>96</v>
       </c>
@@ -5417,7 +9128,7 @@
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="53" t="s">
         <v>78</v>
       </c>
       <c r="C9" s="25">
@@ -5433,7 +9144,7 @@
       <c r="G9" s="22"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="61"/>
+      <c r="B10" s="75"/>
       <c r="C10" s="25">
         <v>4</v>
       </c>
@@ -5447,7 +9158,7 @@
       <c r="G10" s="22"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="55" t="s">
         <v>75</v>
       </c>
       <c r="C11" s="23">
@@ -5463,7 +9174,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="42"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="23">
         <v>7</v>
       </c>
@@ -5477,7 +9188,7 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="42"/>
+      <c r="B13" s="55"/>
       <c r="C13" s="23">
         <v>8</v>
       </c>
@@ -5491,7 +9202,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
+      <c r="B14" s="55"/>
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -5537,11 +9248,11 @@
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
       <c r="E17" s="10">
         <f>SUM(E6:E16)</f>
         <v>100</v>
@@ -5550,16 +9261,1324 @@
         <f>SUM(F6:F9)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="16"/>
+      <c r="G17" s="16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="C21" s="47"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="52"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="18">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="4">
+        <v>15</v>
+      </c>
+      <c r="F24" s="4">
+        <v>15</v>
+      </c>
+      <c r="G24" s="15"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" s="3">
+        <v>5</v>
+      </c>
+      <c r="F25" s="3">
+        <v>5</v>
+      </c>
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="65"/>
+      <c r="C26" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
+        <v>5</v>
+      </c>
+      <c r="G26" s="11"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="25">
+        <v>2</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="29">
+        <v>5</v>
+      </c>
+      <c r="F27" s="29">
+        <v>5</v>
+      </c>
+      <c r="G27" s="22"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="75"/>
+      <c r="C28" s="25">
+        <v>4</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="29">
+        <v>5</v>
+      </c>
+      <c r="F28" s="29">
+        <v>5</v>
+      </c>
+      <c r="G28" s="22"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="23">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" s="3">
+        <v>10</v>
+      </c>
+      <c r="F29" s="3">
+        <v>10</v>
+      </c>
+      <c r="G29" s="11"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="55"/>
+      <c r="C30" s="23">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E30" s="3">
+        <v>10</v>
+      </c>
+      <c r="F30" s="3">
+        <v>10</v>
+      </c>
+      <c r="G30" s="11"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="55"/>
+      <c r="C31" s="23">
+        <v>8</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="3">
+        <v>10</v>
+      </c>
+      <c r="F31" s="37">
+        <v>5</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="55"/>
+      <c r="C32" s="2">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E32" s="3">
+        <v>15</v>
+      </c>
+      <c r="F32" s="3">
+        <v>15</v>
+      </c>
+      <c r="G32" s="11"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="30">
+        <v>2</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="4">
+        <v>5</v>
+      </c>
+      <c r="F33" s="4">
+        <v>5</v>
+      </c>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="2">
+        <v>10</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="3">
+        <v>15</v>
+      </c>
+      <c r="F34" s="3">
+        <v>15</v>
+      </c>
+      <c r="G34" s="11"/>
+    </row>
+    <row r="35" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="57"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="10">
+        <f>SUM(E24:E34)</f>
+        <v>100</v>
+      </c>
+      <c r="F35" s="33">
+        <f>SUM(F24:F34)</f>
+        <v>95</v>
+      </c>
+      <c r="G35" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="47"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="49"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="51"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="52"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="18">
+        <v>1</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E41" s="4">
+        <v>15</v>
+      </c>
+      <c r="F41" s="44">
+        <v>15</v>
+      </c>
+      <c r="G41" s="15"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5</v>
+      </c>
+      <c r="F42" s="37">
+        <v>0</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="65"/>
+      <c r="C43" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5</v>
+      </c>
+      <c r="F43" s="37">
+        <v>2.5</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="25">
+        <v>2</v>
+      </c>
+      <c r="D44" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="29">
+        <v>5</v>
+      </c>
+      <c r="F44" s="43">
+        <v>5</v>
+      </c>
+      <c r="G44" s="22"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="75"/>
+      <c r="C45" s="25">
+        <v>4</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E45" s="29">
+        <v>5</v>
+      </c>
+      <c r="F45" s="38">
+        <v>2.5</v>
+      </c>
+      <c r="G45" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C46" s="23">
+        <v>6</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10</v>
+      </c>
+      <c r="F46" s="41">
+        <v>10</v>
+      </c>
+      <c r="G46" s="11"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="55"/>
+      <c r="C47" s="23">
+        <v>7</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" s="3">
+        <v>10</v>
+      </c>
+      <c r="F47" s="41">
+        <v>10</v>
+      </c>
+      <c r="G47" s="11"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="55"/>
+      <c r="C48" s="23">
+        <v>8</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10</v>
+      </c>
+      <c r="F48" s="41">
+        <v>10</v>
+      </c>
+      <c r="G48" s="11"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="55"/>
+      <c r="C49" s="2">
+        <v>9</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E49" s="3">
+        <v>15</v>
+      </c>
+      <c r="F49" s="41">
+        <v>15</v>
+      </c>
+      <c r="G49" s="11"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="30">
+        <v>2</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E50" s="4">
+        <v>5</v>
+      </c>
+      <c r="F50" s="44">
+        <v>5</v>
+      </c>
+      <c r="G50" s="15"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C51" s="2">
+        <v>10</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E51" s="3">
+        <v>15</v>
+      </c>
+      <c r="F51" s="41">
+        <v>15</v>
+      </c>
+      <c r="G51" s="11"/>
+    </row>
+    <row r="52" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="57"/>
+      <c r="D52" s="58"/>
+      <c r="E52" s="10">
+        <f>SUM(E41:E51)</f>
+        <v>100</v>
+      </c>
+      <c r="F52" s="33">
+        <f>SUM(F41:F51)</f>
+        <v>90</v>
+      </c>
+      <c r="G52" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="C56" s="47"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="49"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="51"/>
+      <c r="D57" s="51"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="51"/>
+      <c r="G57" s="52"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="18">
+        <v>1</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" s="4">
+        <v>15</v>
+      </c>
+      <c r="F59" s="44">
+        <v>15</v>
+      </c>
+      <c r="G59" s="15"/>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5</v>
+      </c>
+      <c r="F60" s="41">
+        <v>5</v>
+      </c>
+      <c r="G60" s="11"/>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B61" s="65"/>
+      <c r="C61" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5</v>
+      </c>
+      <c r="F61" s="41">
+        <v>5</v>
+      </c>
+      <c r="G61" s="11"/>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" s="25">
+        <v>2</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E62" s="29">
+        <v>5</v>
+      </c>
+      <c r="F62" s="43">
+        <v>5</v>
+      </c>
+      <c r="G62" s="22"/>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B63" s="75"/>
+      <c r="C63" s="25">
+        <v>4</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E63" s="29">
+        <v>5</v>
+      </c>
+      <c r="F63" s="38">
+        <v>2.5</v>
+      </c>
+      <c r="G63" s="22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B64" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C64" s="23">
+        <v>6</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E64" s="3">
+        <v>10</v>
+      </c>
+      <c r="F64" s="41">
+        <v>10</v>
+      </c>
+      <c r="G64" s="11"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="55"/>
+      <c r="C65" s="23">
+        <v>7</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E65" s="3">
+        <v>10</v>
+      </c>
+      <c r="F65" s="37">
+        <v>0</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="55"/>
+      <c r="C66" s="23">
+        <v>8</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10</v>
+      </c>
+      <c r="F66" s="41">
+        <v>10</v>
+      </c>
+      <c r="G66" s="11"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="55"/>
+      <c r="C67" s="2">
+        <v>9</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E67" s="3">
+        <v>15</v>
+      </c>
+      <c r="F67" s="41">
+        <v>15</v>
+      </c>
+      <c r="G67" s="11"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="30">
+        <v>2</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E68" s="4">
+        <v>5</v>
+      </c>
+      <c r="F68" s="44">
+        <v>5</v>
+      </c>
+      <c r="G68" s="15"/>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" s="2">
+        <v>10</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E69" s="3">
+        <v>15</v>
+      </c>
+      <c r="F69" s="37">
+        <v>0</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="57"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="10">
+        <f>SUM(E59:E69)</f>
+        <v>100</v>
+      </c>
+      <c r="F70" s="33">
+        <f>SUM(F59:F69)</f>
+        <v>72.5</v>
+      </c>
+      <c r="G70" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B74" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="C74" s="47"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="49"/>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B75" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="51"/>
+      <c r="D75" s="51"/>
+      <c r="E75" s="51"/>
+      <c r="F75" s="51"/>
+      <c r="G75" s="52"/>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C77" s="18">
+        <v>1</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E77" s="4">
+        <v>15</v>
+      </c>
+      <c r="F77" s="44">
+        <v>15</v>
+      </c>
+      <c r="G77" s="15"/>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E78" s="3">
+        <v>5</v>
+      </c>
+      <c r="F78" s="41">
+        <v>5</v>
+      </c>
+      <c r="G78" s="11"/>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="65"/>
+      <c r="C79" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E79" s="3">
+        <v>5</v>
+      </c>
+      <c r="F79" s="41">
+        <v>5</v>
+      </c>
+      <c r="G79" s="11"/>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C80" s="25">
+        <v>2</v>
+      </c>
+      <c r="D80" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E80" s="29">
+        <v>5</v>
+      </c>
+      <c r="F80" s="43">
+        <v>5</v>
+      </c>
+      <c r="G80" s="22"/>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B81" s="75"/>
+      <c r="C81" s="25">
+        <v>4</v>
+      </c>
+      <c r="D81" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E81" s="29">
+        <v>5</v>
+      </c>
+      <c r="F81" s="43">
+        <v>5</v>
+      </c>
+      <c r="G81" s="22"/>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C82" s="23">
+        <v>6</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E82" s="3">
+        <v>10</v>
+      </c>
+      <c r="F82" s="37">
+        <v>0</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B83" s="55"/>
+      <c r="C83" s="23">
+        <v>7</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E83" s="3">
+        <v>10</v>
+      </c>
+      <c r="F83" s="41">
+        <v>10</v>
+      </c>
+      <c r="G83" s="11"/>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B84" s="55"/>
+      <c r="C84" s="23">
+        <v>8</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E84" s="3">
+        <v>10</v>
+      </c>
+      <c r="F84" s="37">
+        <v>0</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B85" s="55"/>
+      <c r="C85" s="2">
+        <v>9</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E85" s="3">
+        <v>15</v>
+      </c>
+      <c r="F85" s="37">
+        <v>0</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B86" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C86" s="30">
+        <v>2</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E86" s="4">
+        <v>5</v>
+      </c>
+      <c r="F86" s="44">
+        <v>5</v>
+      </c>
+      <c r="G86" s="15"/>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B87" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C87" s="2">
+        <v>10</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E87" s="3">
+        <v>15</v>
+      </c>
+      <c r="F87" s="37">
+        <v>0</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B88" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" s="57"/>
+      <c r="D88" s="58"/>
+      <c r="E88" s="10">
+        <f>SUM(E77:E87)</f>
+        <v>100</v>
+      </c>
+      <c r="F88" s="33">
+        <f>SUM(F77:F87)</f>
+        <v>50</v>
+      </c>
+      <c r="G88" s="34" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B92" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="C92" s="47"/>
+      <c r="D92" s="48"/>
+      <c r="E92" s="48"/>
+      <c r="F92" s="48"/>
+      <c r="G92" s="49"/>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B93" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="51"/>
+      <c r="D93" s="51"/>
+      <c r="E93" s="51"/>
+      <c r="F93" s="51"/>
+      <c r="G93" s="52"/>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B94" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C94" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B95" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C95" s="18">
+        <v>1</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E95" s="4">
+        <v>15</v>
+      </c>
+      <c r="F95" s="36">
+        <v>10</v>
+      </c>
+      <c r="G95" s="15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B96" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C96" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E96" s="3">
+        <v>5</v>
+      </c>
+      <c r="F96" s="41">
+        <v>5</v>
+      </c>
+      <c r="G96" s="11"/>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B97" s="65"/>
+      <c r="C97" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E97" s="3">
+        <v>5</v>
+      </c>
+      <c r="F97" s="41">
+        <v>5</v>
+      </c>
+      <c r="G97" s="11"/>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B98" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C98" s="25">
+        <v>2</v>
+      </c>
+      <c r="D98" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E98" s="29">
+        <v>5</v>
+      </c>
+      <c r="F98" s="38">
+        <v>0</v>
+      </c>
+      <c r="G98" s="22" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B99" s="75"/>
+      <c r="C99" s="25">
+        <v>4</v>
+      </c>
+      <c r="D99" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E99" s="29">
+        <v>5</v>
+      </c>
+      <c r="F99" s="43">
+        <v>5</v>
+      </c>
+      <c r="G99" s="22"/>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B100" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C100" s="23">
+        <v>6</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E100" s="3">
+        <v>10</v>
+      </c>
+      <c r="F100" s="41">
+        <v>10</v>
+      </c>
+      <c r="G100" s="11"/>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B101" s="55"/>
+      <c r="C101" s="23">
+        <v>7</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E101" s="3">
+        <v>10</v>
+      </c>
+      <c r="F101" s="37">
+        <v>0</v>
+      </c>
+      <c r="G101" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B102" s="55"/>
+      <c r="C102" s="23">
+        <v>8</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E102" s="3">
+        <v>10</v>
+      </c>
+      <c r="F102" s="37">
+        <v>0</v>
+      </c>
+      <c r="G102" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B103" s="55"/>
+      <c r="C103" s="2">
+        <v>9</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E103" s="3">
+        <v>15</v>
+      </c>
+      <c r="F103" s="37">
+        <v>10</v>
+      </c>
+      <c r="G103" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B104" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C104" s="30">
+        <v>2</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E104" s="4">
+        <v>5</v>
+      </c>
+      <c r="F104" s="36">
+        <v>0</v>
+      </c>
+      <c r="G104" s="15" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B105" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C105" s="2">
+        <v>10</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E105" s="3">
+        <v>15</v>
+      </c>
+      <c r="F105" s="37">
+        <v>0</v>
+      </c>
+      <c r="G105" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B106" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C106" s="57"/>
+      <c r="D106" s="58"/>
+      <c r="E106" s="10">
+        <f>SUM(E95:E105)</f>
+        <v>100</v>
+      </c>
+      <c r="F106" s="42">
+        <f>SUM(F95:F105)</f>
+        <v>45</v>
+      </c>
+      <c r="G106" s="34" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F107" s="40" t="s">
+        <v>159</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="36">
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B32"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B92:G92"/>
+    <mergeCell ref="B93:G93"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Avaliação.xlsx
+++ b/Avaliação.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CST\SOMATIVA1\APW-SOMATIVA-BACK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CST\APW-SOMATIVA-BACK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A0E930-633B-4D55-8064-B2BA2727FC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2BF3B0-C537-41ED-B20F-EE4FFED8CE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ENTREGAS" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="200">
   <si>
     <t>item</t>
   </si>
@@ -359,27 +359,6 @@
     <t>aluno: Camila Tamires — A2</t>
   </si>
   <si>
-    <t>API com trechos truncados; execução incerta. Considerado parcial.</t>
-  </si>
-  <si>
-    <t>Sem regras específicas para Inspeção (apenas IsAuthenticated).</t>
-  </si>
-  <si>
-    <t>Sem regras específicas para Produção (apenas IsAuthenticated).</t>
-  </si>
-  <si>
-    <t>Sem regras específicas para Manutenção (apenas IsAuthenticated).</t>
-  </si>
-  <si>
-    <t>Endpoint de máquinas em manutenção (≥3 meses) não localizado.</t>
-  </si>
-  <si>
-    <t>Endpoint de dashboards do líder não localizado.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>CRITÉRIOS SOMATIVA B1</t>
   </si>
   <si>
@@ -654,6 +633,15 @@
   </si>
   <si>
     <t>Perguntas: 5/5.0</t>
+  </si>
+  <si>
+    <t>aluno: Bruno — A2</t>
+  </si>
+  <si>
+    <t>aluno: Eduardo Diniz — A2</t>
+  </si>
+  <si>
+    <t>não criou serializer para read e write</t>
   </si>
 </sst>
 </file>
@@ -1729,6 +1717,15 @@
     <xf numFmtId="0" fontId="1" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1738,22 +1735,13 @@
     <xf numFmtId="0" fontId="1" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="37" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="37" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1761,16 +1749,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1778,11 +1756,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="37" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2260,7 +2248,7 @@
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D21" s="12"/>
     </row>
@@ -2453,14 +2441,14 @@
       <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
+      <c r="B4" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -2515,7 +2503,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C8" s="27">
@@ -2531,7 +2519,7 @@
       <c r="G8" s="22"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="54"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="24">
         <v>4</v>
       </c>
@@ -2545,7 +2533,7 @@
       <c r="G9" s="22"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="23">
@@ -2561,7 +2549,7 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="55"/>
+      <c r="B11" s="56"/>
       <c r="C11" s="23">
         <v>6</v>
       </c>
@@ -2575,7 +2563,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -2589,7 +2577,7 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="55"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -2603,7 +2591,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="55"/>
+      <c r="B14" s="56"/>
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -2617,7 +2605,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="55"/>
+      <c r="B15" s="56"/>
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -2647,11 +2635,11 @@
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="58"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="52"/>
       <c r="E17" s="10">
         <f>SUM(E6:E16)</f>
         <v>100</v>
@@ -2665,7 +2653,7 @@
     <row r="19" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="46" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C20" s="47"/>
       <c r="D20" s="48"/>
@@ -2674,14 +2662,14 @@
       <c r="G20" s="49"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
+      <c r="B21" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
@@ -2729,7 +2717,7 @@
         <v>81</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E24" s="3">
         <v>10</v>
@@ -2738,11 +2726,11 @@
         <v>0</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="53" t="s">
+      <c r="B25" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C25" s="27">
@@ -2760,7 +2748,7 @@
       <c r="G25" s="22"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="54"/>
+      <c r="B26" s="58"/>
       <c r="C26" s="24">
         <v>4</v>
       </c>
@@ -2776,7 +2764,7 @@
       <c r="G26" s="22"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C27" s="23">
@@ -2794,7 +2782,7 @@
       <c r="G27" s="11"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="55"/>
+      <c r="B28" s="56"/>
       <c r="C28" s="23">
         <v>6</v>
       </c>
@@ -2810,7 +2798,7 @@
       <c r="G28" s="11"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="55"/>
+      <c r="B29" s="56"/>
       <c r="C29" s="2">
         <v>7</v>
       </c>
@@ -2826,7 +2814,7 @@
       <c r="G29" s="11"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="55"/>
+      <c r="B30" s="56"/>
       <c r="C30" s="2">
         <v>8</v>
       </c>
@@ -2842,7 +2830,7 @@
       <c r="G30" s="11"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="55"/>
+      <c r="B31" s="56"/>
       <c r="C31" s="2">
         <v>9</v>
       </c>
@@ -2858,7 +2846,7 @@
       <c r="G31" s="11"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="55"/>
+      <c r="B32" s="56"/>
       <c r="C32" s="2">
         <v>10</v>
       </c>
@@ -2872,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
@@ -2894,11 +2882,11 @@
       <c r="G33" s="15"/>
     </row>
     <row r="34" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="56" t="s">
+      <c r="B34" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="57"/>
-      <c r="D34" s="58"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="10">
         <f>SUM(E23:E33)</f>
         <v>100</v>
@@ -2908,13 +2896,13 @@
         <v>75</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="46" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C37" s="47"/>
       <c r="D37" s="48"/>
@@ -2923,14 +2911,14 @@
       <c r="G37" s="49"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="52"/>
+      <c r="B38" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="55"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
@@ -2978,7 +2966,7 @@
         <v>81</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E41" s="3">
         <v>10</v>
@@ -2987,11 +2975,11 @@
         <v>0</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="53" t="s">
+      <c r="B42" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C42" s="27">
@@ -3007,11 +2995,11 @@
         <v>5</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="54"/>
+      <c r="B43" s="58"/>
       <c r="C43" s="24">
         <v>4</v>
       </c>
@@ -3027,7 +3015,7 @@
       <c r="G43" s="22"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="55" t="s">
+      <c r="B44" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C44" s="23">
@@ -3045,7 +3033,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="55"/>
+      <c r="B45" s="56"/>
       <c r="C45" s="23">
         <v>6</v>
       </c>
@@ -3061,7 +3049,7 @@
       <c r="G45" s="11"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="55"/>
+      <c r="B46" s="56"/>
       <c r="C46" s="2">
         <v>7</v>
       </c>
@@ -3077,7 +3065,7 @@
       <c r="G46" s="11"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="55"/>
+      <c r="B47" s="56"/>
       <c r="C47" s="2">
         <v>8</v>
       </c>
@@ -3093,7 +3081,7 @@
       <c r="G47" s="11"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="55"/>
+      <c r="B48" s="56"/>
       <c r="C48" s="2">
         <v>9</v>
       </c>
@@ -3109,7 +3097,7 @@
       <c r="G48" s="11"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="55"/>
+      <c r="B49" s="56"/>
       <c r="C49" s="2">
         <v>10</v>
       </c>
@@ -3143,11 +3131,11 @@
       <c r="G50" s="15"/>
     </row>
     <row r="51" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="56" t="s">
+      <c r="B51" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C51" s="57"/>
-      <c r="D51" s="58"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="52"/>
       <c r="E51" s="10">
         <f>SUM(E40:E50)</f>
         <v>100</v>
@@ -3157,13 +3145,13 @@
         <v>60</v>
       </c>
       <c r="G51" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B54" s="46" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C54" s="47"/>
       <c r="D54" s="48"/>
@@ -3172,14 +3160,14 @@
       <c r="G54" s="49"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B55" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="51"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="51"/>
-      <c r="G55" s="52"/>
+      <c r="B55" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="55"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="9" t="s">
@@ -3227,7 +3215,7 @@
         <v>81</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E58" s="3">
         <v>10</v>
@@ -3238,7 +3226,7 @@
       <c r="G58" s="11"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B59" s="53" t="s">
+      <c r="B59" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C59" s="27">
@@ -3254,11 +3242,11 @@
         <v>5</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B60" s="54"/>
+      <c r="B60" s="58"/>
       <c r="C60" s="24">
         <v>4</v>
       </c>
@@ -3274,7 +3262,7 @@
       <c r="G60" s="22"/>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B61" s="55" t="s">
+      <c r="B61" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C61" s="23">
@@ -3292,7 +3280,7 @@
       <c r="G61" s="11"/>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B62" s="55"/>
+      <c r="B62" s="56"/>
       <c r="C62" s="23">
         <v>6</v>
       </c>
@@ -3308,7 +3296,7 @@
       <c r="G62" s="11"/>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B63" s="55"/>
+      <c r="B63" s="56"/>
       <c r="C63" s="2">
         <v>7</v>
       </c>
@@ -3324,7 +3312,7 @@
       <c r="G63" s="11"/>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B64" s="55"/>
+      <c r="B64" s="56"/>
       <c r="C64" s="2">
         <v>8</v>
       </c>
@@ -3340,7 +3328,7 @@
       <c r="G64" s="11"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B65" s="55"/>
+      <c r="B65" s="56"/>
       <c r="C65" s="2">
         <v>9</v>
       </c>
@@ -3356,7 +3344,7 @@
       <c r="G65" s="11"/>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="55"/>
+      <c r="B66" s="56"/>
       <c r="C66" s="2">
         <v>10</v>
       </c>
@@ -3390,11 +3378,11 @@
       <c r="G67" s="15"/>
     </row>
     <row r="68" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="56" t="s">
+      <c r="B68" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="57"/>
-      <c r="D68" s="58"/>
+      <c r="C68" s="51"/>
+      <c r="D68" s="52"/>
       <c r="E68" s="10">
         <f>SUM(E57:E67)</f>
         <v>100</v>
@@ -3404,13 +3392,13 @@
         <v>95</v>
       </c>
       <c r="G68" s="34" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="72" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B72" s="46" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C72" s="47"/>
       <c r="D72" s="48"/>
@@ -3419,14 +3407,14 @@
       <c r="G72" s="49"/>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B73" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="51"/>
-      <c r="D73" s="51"/>
-      <c r="E73" s="51"/>
-      <c r="F73" s="51"/>
-      <c r="G73" s="52"/>
+      <c r="B73" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="54"/>
+      <c r="D73" s="54"/>
+      <c r="E73" s="54"/>
+      <c r="F73" s="54"/>
+      <c r="G73" s="55"/>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B74" s="9" t="s">
@@ -3474,7 +3462,7 @@
         <v>81</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E76" s="3">
         <v>10</v>
@@ -3485,7 +3473,7 @@
       <c r="G76" s="11"/>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B77" s="53" t="s">
+      <c r="B77" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C77" s="27">
@@ -3503,7 +3491,7 @@
       <c r="G77" s="22"/>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B78" s="54"/>
+      <c r="B78" s="58"/>
       <c r="C78" s="24">
         <v>4</v>
       </c>
@@ -3519,7 +3507,7 @@
       <c r="G78" s="22"/>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B79" s="55" t="s">
+      <c r="B79" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C79" s="23">
@@ -3537,7 +3525,7 @@
       <c r="G79" s="11"/>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B80" s="55"/>
+      <c r="B80" s="56"/>
       <c r="C80" s="23">
         <v>6</v>
       </c>
@@ -3547,11 +3535,13 @@
       <c r="E80" s="3">
         <v>5</v>
       </c>
-      <c r="F80" s="41"/>
+      <c r="F80" s="41">
+        <v>5</v>
+      </c>
       <c r="G80" s="11"/>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B81" s="55"/>
+      <c r="B81" s="56"/>
       <c r="C81" s="2">
         <v>7</v>
       </c>
@@ -3561,11 +3551,13 @@
       <c r="E81" s="3">
         <v>5</v>
       </c>
-      <c r="F81" s="41"/>
+      <c r="F81" s="41">
+        <v>5</v>
+      </c>
       <c r="G81" s="11"/>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="55"/>
+      <c r="B82" s="56"/>
       <c r="C82" s="2">
         <v>8</v>
       </c>
@@ -3575,11 +3567,13 @@
       <c r="E82" s="3">
         <v>5</v>
       </c>
-      <c r="F82" s="41"/>
+      <c r="F82" s="41">
+        <v>5</v>
+      </c>
       <c r="G82" s="11"/>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B83" s="55"/>
+      <c r="B83" s="56"/>
       <c r="C83" s="2">
         <v>9</v>
       </c>
@@ -3589,11 +3583,13 @@
       <c r="E83" s="3">
         <v>15</v>
       </c>
-      <c r="F83" s="41"/>
+      <c r="F83" s="41">
+        <v>15</v>
+      </c>
       <c r="G83" s="11"/>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B84" s="55"/>
+      <c r="B84" s="56"/>
       <c r="C84" s="2">
         <v>10</v>
       </c>
@@ -3603,7 +3599,9 @@
       <c r="E84" s="3">
         <v>15</v>
       </c>
-      <c r="F84" s="41"/>
+      <c r="F84" s="41">
+        <v>15</v>
+      </c>
       <c r="G84" s="11"/>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.25">
@@ -3619,54 +3617,56 @@
       <c r="E85" s="4">
         <v>5</v>
       </c>
-      <c r="F85" s="44"/>
+      <c r="F85" s="44">
+        <v>5</v>
+      </c>
       <c r="G85" s="15"/>
     </row>
     <row r="86" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="56" t="s">
+      <c r="B86" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C86" s="57"/>
-      <c r="D86" s="58"/>
+      <c r="C86" s="51"/>
+      <c r="D86" s="52"/>
       <c r="E86" s="10">
         <f>SUM(E75:E85)</f>
         <v>100</v>
       </c>
       <c r="F86" s="45">
         <f>SUM(F75:F85)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G86" s="34" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="B79:B84"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="B61:B66"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B49"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B27:B32"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B10:B15"/>
     <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B27:B32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B49"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="B61:B66"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="B79:B84"/>
-    <mergeCell ref="B86:D86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3675,7 +3675,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78084D1B-51A4-4C2A-88A0-B41341084014}">
-  <dimension ref="B2:G34"/>
+  <dimension ref="B2:G69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3700,14 +3700,14 @@
       <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
+      <c r="B4" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -3746,7 +3746,7 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="23" t="s">
@@ -3762,7 +3762,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="65"/>
+      <c r="B8" s="73"/>
       <c r="C8" s="23" t="s">
         <v>89</v>
       </c>
@@ -3776,7 +3776,7 @@
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C9" s="27">
@@ -3792,7 +3792,7 @@
       <c r="G9" s="22"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="54"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="24">
         <v>5</v>
       </c>
@@ -3806,7 +3806,7 @@
       <c r="G10" s="22"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C11" s="23">
@@ -3822,7 +3822,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -3836,7 +3836,7 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="55"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -3850,7 +3850,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="55"/>
+      <c r="B14" s="56"/>
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -3864,7 +3864,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="55"/>
+      <c r="B15" s="56"/>
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -3894,17 +3894,17 @@
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="58"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="52"/>
       <c r="E17" s="10">
         <f>SUM(E6:E16)</f>
         <v>100</v>
       </c>
       <c r="F17" s="10">
-        <f>SUM(F6:F9)</f>
+        <f>SUM(F6:F16)</f>
         <v>0</v>
       </c>
       <c r="G17" s="16"/>
@@ -3914,21 +3914,21 @@
       <c r="B20" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="66"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="67"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="63"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="70"/>
+      <c r="B21" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="65"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="66"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
@@ -3943,8 +3943,8 @@
       <c r="E22" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F22" s="2">
-        <v>15</v>
+      <c r="F22" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="G22" s="14" t="s">
         <v>2</v>
@@ -3964,12 +3964,12 @@
         <v>15</v>
       </c>
       <c r="F23" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G23" s="15"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="62" t="s">
+      <c r="B24" s="67" t="s">
         <v>71</v>
       </c>
       <c r="C24" s="23" t="s">
@@ -3987,7 +3987,7 @@
       <c r="G24" s="11"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="63"/>
+      <c r="B25" s="68"/>
       <c r="C25" s="23" t="s">
         <v>89</v>
       </c>
@@ -3998,14 +3998,12 @@
         <v>5</v>
       </c>
       <c r="F25" s="3">
-        <v>6</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>105</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="71" t="s">
+      <c r="B26" s="69" t="s">
         <v>78</v>
       </c>
       <c r="C26" s="27">
@@ -4023,7 +4021,7 @@
       <c r="G26" s="22"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="63"/>
+      <c r="B27" s="68"/>
       <c r="C27" s="24">
         <v>5</v>
       </c>
@@ -4034,14 +4032,12 @@
         <v>10</v>
       </c>
       <c r="F27" s="29">
-        <v>0</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>106</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G27" s="22"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C28" s="23">
@@ -4054,14 +4050,12 @@
         <v>6</v>
       </c>
       <c r="F28" s="3">
-        <v>0</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>107</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G28" s="11"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="72"/>
+      <c r="B29" s="70"/>
       <c r="C29" s="2">
         <v>7</v>
       </c>
@@ -4072,14 +4066,12 @@
         <v>6</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>108</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G29" s="11"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="72"/>
+      <c r="B30" s="70"/>
       <c r="C30" s="2">
         <v>8</v>
       </c>
@@ -4090,14 +4082,12 @@
         <v>6</v>
       </c>
       <c r="F30" s="3">
-        <v>0</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>109</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G30" s="11"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="72"/>
+      <c r="B31" s="70"/>
       <c r="C31" s="2">
         <v>9</v>
       </c>
@@ -4108,14 +4098,12 @@
         <v>16</v>
       </c>
       <c r="F31" s="3">
-        <v>0</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>110</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G31" s="11"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="73"/>
+      <c r="B32" s="71"/>
       <c r="C32" s="2">
         <v>10</v>
       </c>
@@ -4126,7 +4114,7 @@
         <v>16</v>
       </c>
       <c r="F32" s="3">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G32" s="11"/>
     </row>
@@ -4144,7 +4132,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="4">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="G33" s="15"/>
     </row>
@@ -4154,21 +4142,504 @@
       </c>
       <c r="C34" s="60"/>
       <c r="D34" s="61"/>
-      <c r="E34" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>111</v>
+      <c r="E34" s="10">
+        <f>SUM(E23:E33)</f>
+        <v>100</v>
+      </c>
+      <c r="F34" s="10">
+        <f>SUM(F23:F33)</f>
+        <v>100</v>
       </c>
       <c r="G34" s="16"/>
     </row>
+    <row r="37" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="63"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="65"/>
+      <c r="F39" s="65"/>
+      <c r="G39" s="66"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="18">
+        <v>1</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E41" s="4">
+        <v>15</v>
+      </c>
+      <c r="F41" s="4">
+        <v>15</v>
+      </c>
+      <c r="G41" s="15"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5</v>
+      </c>
+      <c r="F42" s="3">
+        <v>5</v>
+      </c>
+      <c r="G42" s="11"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="68"/>
+      <c r="C43" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3">
+        <v>5</v>
+      </c>
+      <c r="G43" s="11"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="27">
+        <v>2</v>
+      </c>
+      <c r="D44" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="29">
+        <v>10</v>
+      </c>
+      <c r="F44" s="29">
+        <v>10</v>
+      </c>
+      <c r="G44" s="22"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="68"/>
+      <c r="C45" s="24">
+        <v>5</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E45" s="29">
+        <v>10</v>
+      </c>
+      <c r="F45" s="29">
+        <v>10</v>
+      </c>
+      <c r="G45" s="22"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="C46" s="23">
+        <v>6</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6</v>
+      </c>
+      <c r="F46" s="3">
+        <v>6</v>
+      </c>
+      <c r="G46" s="11"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="70"/>
+      <c r="C47" s="2">
+        <v>7</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6</v>
+      </c>
+      <c r="F47" s="3">
+        <v>6</v>
+      </c>
+      <c r="G47" s="11"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="70"/>
+      <c r="C48" s="2">
+        <v>8</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3">
+        <v>6</v>
+      </c>
+      <c r="G48" s="11"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="70"/>
+      <c r="C49" s="2">
+        <v>9</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E49" s="3">
+        <v>16</v>
+      </c>
+      <c r="F49" s="3">
+        <v>16</v>
+      </c>
+      <c r="G49" s="11"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="71"/>
+      <c r="C50" s="2">
+        <v>10</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E50" s="3">
+        <v>16</v>
+      </c>
+      <c r="F50" s="3">
+        <v>16</v>
+      </c>
+      <c r="G50" s="11"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="30">
+        <v>2</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" s="4">
+        <v>5</v>
+      </c>
+      <c r="F51" s="4">
+        <v>5</v>
+      </c>
+      <c r="G51" s="15"/>
+    </row>
+    <row r="52" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="60"/>
+      <c r="D52" s="61"/>
+      <c r="E52" s="10">
+        <f>SUM(E41:E51)</f>
+        <v>100</v>
+      </c>
+      <c r="F52" s="10">
+        <f>SUM(F41:F51)</f>
+        <v>100</v>
+      </c>
+      <c r="G52" s="16"/>
+    </row>
+    <row r="54" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="C55" s="62"/>
+      <c r="D55" s="62"/>
+      <c r="E55" s="62"/>
+      <c r="F55" s="62"/>
+      <c r="G55" s="63"/>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="65"/>
+      <c r="D56" s="65"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="66"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" s="18">
+        <v>1</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E58" s="4">
+        <v>15</v>
+      </c>
+      <c r="F58" s="4">
+        <v>15</v>
+      </c>
+      <c r="G58" s="15"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5</v>
+      </c>
+      <c r="F59" s="37">
+        <v>2</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="68"/>
+      <c r="C60" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5</v>
+      </c>
+      <c r="F60" s="37">
+        <v>2</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B61" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="C61" s="27">
+        <v>2</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E61" s="29">
+        <v>10</v>
+      </c>
+      <c r="F61" s="29">
+        <v>10</v>
+      </c>
+      <c r="G61" s="22"/>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="68"/>
+      <c r="C62" s="24">
+        <v>5</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E62" s="29">
+        <v>10</v>
+      </c>
+      <c r="F62" s="29"/>
+      <c r="G62" s="22"/>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B63" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="C63" s="23">
+        <v>6</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E63" s="3">
+        <v>6</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="G63" s="11"/>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B64" s="70"/>
+      <c r="C64" s="2">
+        <v>7</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E64" s="3">
+        <v>6</v>
+      </c>
+      <c r="F64" s="3"/>
+      <c r="G64" s="11"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="70"/>
+      <c r="C65" s="2">
+        <v>8</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E65" s="3">
+        <v>6</v>
+      </c>
+      <c r="F65" s="3"/>
+      <c r="G65" s="11"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="70"/>
+      <c r="C66" s="2">
+        <v>9</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E66" s="3">
+        <v>16</v>
+      </c>
+      <c r="F66" s="3"/>
+      <c r="G66" s="11"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="71"/>
+      <c r="C67" s="2">
+        <v>10</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E67" s="3">
+        <v>16</v>
+      </c>
+      <c r="F67" s="3"/>
+      <c r="G67" s="11"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="30">
+        <v>2</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E68" s="4">
+        <v>5</v>
+      </c>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+      <c r="G68" s="15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" s="60"/>
+      <c r="D69" s="61"/>
+      <c r="E69" s="10">
+        <f>SUM(E58:E68)</f>
+        <v>100</v>
+      </c>
+      <c r="F69" s="10">
+        <f>SUM(F58:F68)</f>
+        <v>29</v>
+      </c>
+      <c r="G69" s="16"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B28:B32"/>
+  <mergeCells count="24">
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="B63:B67"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="B4:G4"/>
@@ -4176,6 +4647,17 @@
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B15"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B28:B32"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B46:B50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4209,14 +4691,14 @@
       <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
+      <c r="B4" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -4255,7 +4737,7 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="23" t="s">
@@ -4285,7 +4767,7 @@
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="65"/>
+      <c r="B9" s="73"/>
       <c r="C9" s="23" t="s">
         <v>96</v>
       </c>
@@ -4299,7 +4781,7 @@
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C10" s="25">
@@ -4329,7 +4811,7 @@
       <c r="G11" s="22"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="54"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="24">
         <v>7</v>
       </c>
@@ -4343,7 +4825,7 @@
       <c r="G12" s="22"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C13" s="23">
@@ -4359,7 +4841,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="55"/>
+      <c r="B14" s="56"/>
       <c r="C14" s="2">
         <v>10</v>
       </c>
@@ -4405,11 +4887,11 @@
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="58"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="52"/>
       <c r="E17" s="10">
         <f>SUM(E6:E16)</f>
         <v>100</v>
@@ -4419,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="46" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C21" s="47"/>
       <c r="D21" s="48"/>
@@ -4434,14 +4916,14 @@
       <c r="G21" s="49"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="52"/>
+      <c r="B22" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="55"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
@@ -4480,7 +4962,7 @@
       <c r="G24" s="15"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="64" t="s">
+      <c r="B25" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C25" s="23" t="s">
@@ -4510,7 +4992,7 @@
       <c r="G26" s="11"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="65"/>
+      <c r="B27" s="73"/>
       <c r="C27" s="23" t="s">
         <v>96</v>
       </c>
@@ -4524,7 +5006,7 @@
       <c r="G27" s="11"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="53" t="s">
+      <c r="B28" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C28" s="25">
@@ -4554,7 +5036,7 @@
       <c r="G29" s="22"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="54"/>
+      <c r="B30" s="58"/>
       <c r="C30" s="24">
         <v>7</v>
       </c>
@@ -4568,7 +5050,7 @@
       <c r="G30" s="22"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="23">
@@ -4584,7 +5066,7 @@
       <c r="G31" s="11"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="55"/>
+      <c r="B32" s="56"/>
       <c r="C32" s="2">
         <v>10</v>
       </c>
@@ -4632,11 +5114,11 @@
       <c r="G34" s="11"/>
     </row>
     <row r="35" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="56" t="s">
+      <c r="B35" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="58"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="52"/>
       <c r="E35" s="10">
         <f>SUM(E24:E34)</f>
         <v>100</v>
@@ -4646,13 +5128,13 @@
         <v>0</v>
       </c>
       <c r="G35" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="46" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C39" s="47"/>
       <c r="D39" s="48"/>
@@ -4661,14 +5143,14 @@
       <c r="G39" s="49"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B40" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="52"/>
+      <c r="B40" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="55"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
@@ -4707,7 +5189,7 @@
       <c r="G42" s="15"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="64" t="s">
+      <c r="B43" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C43" s="23" t="s">
@@ -4737,7 +5219,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="65"/>
+      <c r="B45" s="73"/>
       <c r="C45" s="23" t="s">
         <v>96</v>
       </c>
@@ -4751,7 +5233,7 @@
       <c r="G45" s="11"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="53" t="s">
+      <c r="B46" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C46" s="25">
@@ -4781,7 +5263,7 @@
       <c r="G47" s="22"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="54"/>
+      <c r="B48" s="58"/>
       <c r="C48" s="24">
         <v>7</v>
       </c>
@@ -4795,7 +5277,7 @@
       <c r="G48" s="22"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="55" t="s">
+      <c r="B49" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C49" s="23">
@@ -4811,7 +5293,7 @@
       <c r="G49" s="11"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="55"/>
+      <c r="B50" s="56"/>
       <c r="C50" s="2">
         <v>10</v>
       </c>
@@ -4859,11 +5341,11 @@
       <c r="G52" s="11"/>
     </row>
     <row r="53" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="56" t="s">
+      <c r="B53" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="57"/>
-      <c r="D53" s="58"/>
+      <c r="C53" s="51"/>
+      <c r="D53" s="52"/>
       <c r="E53" s="10">
         <f>SUM(E42:E52)</f>
         <v>100</v>
@@ -4873,13 +5355,13 @@
         <v>0</v>
       </c>
       <c r="G53" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="46" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C56" s="47"/>
       <c r="D56" s="48"/>
@@ -4888,14 +5370,14 @@
       <c r="G56" s="49"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="51"/>
-      <c r="D57" s="51"/>
-      <c r="E57" s="51"/>
-      <c r="F57" s="51"/>
-      <c r="G57" s="52"/>
+      <c r="B57" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="55"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="9" t="s">
@@ -4934,7 +5416,7 @@
       <c r="G59" s="15"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B60" s="64" t="s">
+      <c r="B60" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C60" s="23" t="s">
@@ -4964,7 +5446,7 @@
       <c r="G61" s="11"/>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B62" s="65"/>
+      <c r="B62" s="73"/>
       <c r="C62" s="23" t="s">
         <v>96</v>
       </c>
@@ -4978,7 +5460,7 @@
       <c r="G62" s="11"/>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B63" s="53" t="s">
+      <c r="B63" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C63" s="25">
@@ -5008,7 +5490,7 @@
       <c r="G64" s="22"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B65" s="54"/>
+      <c r="B65" s="58"/>
       <c r="C65" s="24">
         <v>7</v>
       </c>
@@ -5022,7 +5504,7 @@
       <c r="G65" s="22"/>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="55" t="s">
+      <c r="B66" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C66" s="23">
@@ -5038,7 +5520,7 @@
       <c r="G66" s="11"/>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B67" s="55"/>
+      <c r="B67" s="56"/>
       <c r="C67" s="2">
         <v>10</v>
       </c>
@@ -5084,15 +5566,15 @@
         <v>5</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="56" t="s">
+      <c r="B70" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="57"/>
-      <c r="D70" s="58"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="52"/>
       <c r="E70" s="10">
         <f>SUM(E59:E69)</f>
         <v>100</v>
@@ -5102,13 +5584,13 @@
         <v>0</v>
       </c>
       <c r="G70" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="73" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B73" s="46" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C73" s="47"/>
       <c r="D73" s="48"/>
@@ -5117,14 +5599,14 @@
       <c r="G73" s="49"/>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B74" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="51"/>
-      <c r="D74" s="51"/>
-      <c r="E74" s="51"/>
-      <c r="F74" s="51"/>
-      <c r="G74" s="52"/>
+      <c r="B74" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="55"/>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B75" s="9" t="s">
@@ -5163,7 +5645,7 @@
       <c r="G76" s="15"/>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B77" s="64" t="s">
+      <c r="B77" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C77" s="23" t="s">
@@ -5193,7 +5675,7 @@
       <c r="G78" s="11"/>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B79" s="65"/>
+      <c r="B79" s="73"/>
       <c r="C79" s="23" t="s">
         <v>96</v>
       </c>
@@ -5207,7 +5689,7 @@
       <c r="G79" s="11"/>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B80" s="53" t="s">
+      <c r="B80" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C80" s="25">
@@ -5237,7 +5719,7 @@
       <c r="G81" s="22"/>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="54"/>
+      <c r="B82" s="58"/>
       <c r="C82" s="24">
         <v>7</v>
       </c>
@@ -5251,7 +5733,7 @@
       <c r="G82" s="22"/>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B83" s="55" t="s">
+      <c r="B83" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C83" s="23">
@@ -5267,7 +5749,7 @@
       <c r="G83" s="11"/>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B84" s="55"/>
+      <c r="B84" s="56"/>
       <c r="C84" s="2">
         <v>10</v>
       </c>
@@ -5313,15 +5795,15 @@
         <v>5</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="56" t="s">
+      <c r="B87" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C87" s="57"/>
-      <c r="D87" s="58"/>
+      <c r="C87" s="51"/>
+      <c r="D87" s="52"/>
       <c r="E87" s="10">
         <f>SUM(E76:E86)</f>
         <v>100</v>
@@ -5331,13 +5813,13 @@
         <v>0</v>
       </c>
       <c r="G87" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="89" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="90" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B90" s="46" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C90" s="47"/>
       <c r="D90" s="48"/>
@@ -5346,14 +5828,14 @@
       <c r="G90" s="49"/>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B91" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91" s="51"/>
-      <c r="D91" s="51"/>
-      <c r="E91" s="51"/>
-      <c r="F91" s="51"/>
-      <c r="G91" s="52"/>
+      <c r="B91" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="54"/>
+      <c r="D91" s="54"/>
+      <c r="E91" s="54"/>
+      <c r="F91" s="54"/>
+      <c r="G91" s="55"/>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B92" s="9" t="s">
@@ -5392,7 +5874,7 @@
       <c r="G93" s="15"/>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B94" s="64" t="s">
+      <c r="B94" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C94" s="23" t="s">
@@ -5422,7 +5904,7 @@
       <c r="G95" s="11"/>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B96" s="65"/>
+      <c r="B96" s="73"/>
       <c r="C96" s="23" t="s">
         <v>96</v>
       </c>
@@ -5436,7 +5918,7 @@
       <c r="G96" s="11"/>
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B97" s="53" t="s">
+      <c r="B97" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C97" s="25">
@@ -5466,7 +5948,7 @@
       <c r="G98" s="22"/>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B99" s="54"/>
+      <c r="B99" s="58"/>
       <c r="C99" s="24">
         <v>7</v>
       </c>
@@ -5480,7 +5962,7 @@
       <c r="G99" s="22"/>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B100" s="55" t="s">
+      <c r="B100" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C100" s="23">
@@ -5496,7 +5978,7 @@
       <c r="G100" s="11"/>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B101" s="55"/>
+      <c r="B101" s="56"/>
       <c r="C101" s="2">
         <v>10</v>
       </c>
@@ -5544,11 +6026,11 @@
       <c r="G103" s="11"/>
     </row>
     <row r="104" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="56" t="s">
+      <c r="B104" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C104" s="57"/>
-      <c r="D104" s="58"/>
+      <c r="C104" s="51"/>
+      <c r="D104" s="52"/>
       <c r="E104" s="10">
         <f>SUM(E93:E103)</f>
         <v>100</v>
@@ -5558,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="G104" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="107" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B108" s="46" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C108" s="47"/>
       <c r="D108" s="48"/>
@@ -5573,14 +6055,14 @@
       <c r="G108" s="49"/>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B109" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C109" s="51"/>
-      <c r="D109" s="51"/>
-      <c r="E109" s="51"/>
-      <c r="F109" s="51"/>
-      <c r="G109" s="52"/>
+      <c r="B109" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="54"/>
+      <c r="D109" s="54"/>
+      <c r="E109" s="54"/>
+      <c r="F109" s="54"/>
+      <c r="G109" s="55"/>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B110" s="9" t="s">
@@ -5619,7 +6101,7 @@
       <c r="G111" s="15"/>
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B112" s="64" t="s">
+      <c r="B112" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C112" s="23" t="s">
@@ -5649,7 +6131,7 @@
       <c r="G113" s="11"/>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B114" s="65"/>
+      <c r="B114" s="73"/>
       <c r="C114" s="23" t="s">
         <v>96</v>
       </c>
@@ -5663,7 +6145,7 @@
       <c r="G114" s="11"/>
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B115" s="53" t="s">
+      <c r="B115" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C115" s="25">
@@ -5693,7 +6175,7 @@
       <c r="G116" s="22"/>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B117" s="54"/>
+      <c r="B117" s="58"/>
       <c r="C117" s="24">
         <v>7</v>
       </c>
@@ -5707,7 +6189,7 @@
       <c r="G117" s="22"/>
     </row>
     <row r="118" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B118" s="55" t="s">
+      <c r="B118" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C118" s="23">
@@ -5723,7 +6205,7 @@
       <c r="G118" s="11"/>
     </row>
     <row r="119" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B119" s="55"/>
+      <c r="B119" s="56"/>
       <c r="C119" s="2">
         <v>10</v>
       </c>
@@ -5769,15 +6251,15 @@
         <v>5</v>
       </c>
       <c r="G121" s="11" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="122" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="56" t="s">
+      <c r="B122" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C122" s="57"/>
-      <c r="D122" s="58"/>
+      <c r="C122" s="51"/>
+      <c r="D122" s="52"/>
       <c r="E122" s="10">
         <f>SUM(E111:E121)</f>
         <v>100</v>
@@ -5787,53 +6269,53 @@
         <v>0</v>
       </c>
       <c r="G122" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B108:G108"/>
+    <mergeCell ref="B109:G109"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="B91:G91"/>
+    <mergeCell ref="B94:B96"/>
+    <mergeCell ref="B97:B99"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="B90:G90"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B31:B32"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="B63:B65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="B80:B82"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="B90:G90"/>
-    <mergeCell ref="B91:G91"/>
-    <mergeCell ref="B94:B96"/>
-    <mergeCell ref="B97:B99"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B108:G108"/>
-    <mergeCell ref="B109:G109"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="B118:B119"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5858,7 +6340,7 @@
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="46" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C3" s="47"/>
       <c r="D3" s="48"/>
@@ -5867,14 +6349,14 @@
       <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
+      <c r="B4" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -5920,7 +6402,7 @@
         <v>81</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E7" s="3">
         <v>10</v>
@@ -5929,7 +6411,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C8" s="27">
@@ -5945,12 +6427,12 @@
       <c r="G8" s="22"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="54"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="24">
         <v>4</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E9" s="29">
         <v>10</v>
@@ -5959,14 +6441,14 @@
       <c r="G9" s="22"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="23">
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E10" s="3">
         <v>5</v>
@@ -5975,12 +6457,12 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="55"/>
+      <c r="B11" s="56"/>
       <c r="C11" s="23">
         <v>6</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E11" s="3">
         <v>5</v>
@@ -5989,12 +6471,12 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="2">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E12" s="3">
         <v>5</v>
@@ -6003,12 +6485,12 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="55"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="2">
         <v>8</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E13" s="3">
         <v>5</v>
@@ -6017,12 +6499,12 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="55"/>
+      <c r="B14" s="56"/>
       <c r="C14" s="2">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E14" s="3">
         <v>5</v>
@@ -6031,12 +6513,12 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="55"/>
+      <c r="B15" s="56"/>
       <c r="C15" s="2">
         <v>8</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E15" s="3">
         <v>15</v>
@@ -6045,12 +6527,12 @@
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="55"/>
+      <c r="B16" s="56"/>
       <c r="C16" s="2">
         <v>9</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E16" s="3">
         <v>10</v>
@@ -6075,11 +6557,11 @@
       <c r="G17" s="15"/>
     </row>
     <row r="18" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="57"/>
-      <c r="D18" s="58"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="52"/>
       <c r="E18" s="10">
         <f>SUM(E6:E17)</f>
         <v>100</v>
@@ -6093,23 +6575,23 @@
     <row r="21" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="67"/>
+        <v>123</v>
+      </c>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="63"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="70"/>
+      <c r="B23" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="66"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
@@ -6157,7 +6639,7 @@
         <v>81</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E26" s="3">
         <v>10</v>
@@ -6168,7 +6650,7 @@
       <c r="G26" s="11"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="71" t="s">
+      <c r="B27" s="69" t="s">
         <v>78</v>
       </c>
       <c r="C27" s="27">
@@ -6186,12 +6668,12 @@
       <c r="G27" s="22"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="63"/>
+      <c r="B28" s="68"/>
       <c r="C28" s="24">
         <v>4</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E28" s="29">
         <v>10</v>
@@ -6202,14 +6684,14 @@
       <c r="G28" s="22"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C29" s="23">
         <v>5</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E29" s="3">
         <v>5</v>
@@ -6220,12 +6702,12 @@
       <c r="G29" s="11"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="72"/>
+      <c r="B30" s="70"/>
       <c r="C30" s="23">
         <v>6</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E30" s="3">
         <v>5</v>
@@ -6236,12 +6718,12 @@
       <c r="G30" s="11"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="72"/>
+      <c r="B31" s="70"/>
       <c r="C31" s="2">
         <v>7</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E31" s="3">
         <v>5</v>
@@ -6252,12 +6734,12 @@
       <c r="G31" s="11"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="72"/>
+      <c r="B32" s="70"/>
       <c r="C32" s="2">
         <v>8</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E32" s="3">
         <v>5</v>
@@ -6268,12 +6750,12 @@
       <c r="G32" s="11"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="72"/>
+      <c r="B33" s="70"/>
       <c r="C33" s="2">
         <v>10</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E33" s="3">
         <v>5</v>
@@ -6284,12 +6766,12 @@
       <c r="G33" s="11"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="72"/>
+      <c r="B34" s="70"/>
       <c r="C34" s="2">
         <v>8</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E34" s="3">
         <v>15</v>
@@ -6300,12 +6782,12 @@
       <c r="G34" s="11"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="73"/>
+      <c r="B35" s="71"/>
       <c r="C35" s="2">
         <v>9</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E35" s="3">
         <v>10</v>
@@ -6332,7 +6814,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6350,29 +6832,29 @@
         <v>95</v>
       </c>
       <c r="G37" s="34" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="67"/>
+        <v>135</v>
+      </c>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="63"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="70"/>
+      <c r="B41" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="66"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" s="9" t="s">
@@ -6420,7 +6902,7 @@
         <v>81</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E44" s="3">
         <v>10</v>
@@ -6431,7 +6913,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="71" t="s">
+      <c r="B45" s="69" t="s">
         <v>78</v>
       </c>
       <c r="C45" s="27">
@@ -6449,12 +6931,12 @@
       <c r="G45" s="22"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="63"/>
+      <c r="B46" s="68"/>
       <c r="C46" s="24">
         <v>4</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E46" s="29">
         <v>10</v>
@@ -6465,14 +6947,14 @@
       <c r="G46" s="22"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="55" t="s">
+      <c r="B47" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C47" s="23">
         <v>5</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E47" s="3">
         <v>5</v>
@@ -6483,12 +6965,12 @@
       <c r="G47" s="11"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="72"/>
+      <c r="B48" s="70"/>
       <c r="C48" s="23">
         <v>6</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E48" s="3">
         <v>5</v>
@@ -6499,12 +6981,12 @@
       <c r="G48" s="11"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="72"/>
+      <c r="B49" s="70"/>
       <c r="C49" s="2">
         <v>7</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E49" s="3">
         <v>5</v>
@@ -6515,12 +6997,12 @@
       <c r="G49" s="11"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="72"/>
+      <c r="B50" s="70"/>
       <c r="C50" s="2">
         <v>8</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E50" s="3">
         <v>5</v>
@@ -6531,12 +7013,12 @@
       <c r="G50" s="11"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B51" s="72"/>
+      <c r="B51" s="70"/>
       <c r="C51" s="2">
         <v>10</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E51" s="3">
         <v>5</v>
@@ -6547,12 +7029,12 @@
       <c r="G51" s="11"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="72"/>
+      <c r="B52" s="70"/>
       <c r="C52" s="2">
         <v>8</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E52" s="3">
         <v>15</v>
@@ -6561,16 +7043,16 @@
         <v>0</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="73"/>
+      <c r="B53" s="71"/>
       <c r="C53" s="2">
         <v>9</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E53" s="3">
         <v>10</v>
@@ -6613,29 +7095,29 @@
         <v>85</v>
       </c>
       <c r="G55" s="35" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="C58" s="66"/>
-      <c r="D58" s="66"/>
-      <c r="E58" s="66"/>
-      <c r="F58" s="66"/>
-      <c r="G58" s="67"/>
+        <v>124</v>
+      </c>
+      <c r="C58" s="62"/>
+      <c r="D58" s="62"/>
+      <c r="E58" s="62"/>
+      <c r="F58" s="62"/>
+      <c r="G58" s="63"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B59" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="69"/>
-      <c r="D59" s="69"/>
-      <c r="E59" s="69"/>
-      <c r="F59" s="69"/>
-      <c r="G59" s="70"/>
+      <c r="B59" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="65"/>
+      <c r="D59" s="65"/>
+      <c r="E59" s="65"/>
+      <c r="F59" s="65"/>
+      <c r="G59" s="66"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B60" s="9" t="s">
@@ -6674,7 +7156,7 @@
         <v>10</v>
       </c>
       <c r="G61" s="15" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
@@ -6685,7 +7167,7 @@
         <v>81</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E62" s="3">
         <v>10</v>
@@ -6696,7 +7178,7 @@
       <c r="G62" s="11"/>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B63" s="71" t="s">
+      <c r="B63" s="69" t="s">
         <v>78</v>
       </c>
       <c r="C63" s="27">
@@ -6714,12 +7196,12 @@
       <c r="G63" s="22"/>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B64" s="63"/>
+      <c r="B64" s="68"/>
       <c r="C64" s="24">
         <v>4</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E64" s="29">
         <v>10</v>
@@ -6730,14 +7212,14 @@
       <c r="G64" s="22"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B65" s="55" t="s">
+      <c r="B65" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C65" s="23">
         <v>5</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E65" s="3">
         <v>5</v>
@@ -6746,16 +7228,16 @@
         <v>0</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="72"/>
+      <c r="B66" s="70"/>
       <c r="C66" s="23">
         <v>6</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E66" s="3">
         <v>5</v>
@@ -6764,16 +7246,16 @@
         <v>0</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B67" s="72"/>
+      <c r="B67" s="70"/>
       <c r="C67" s="2">
         <v>7</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E67" s="3">
         <v>5</v>
@@ -6782,16 +7264,16 @@
         <v>0</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B68" s="72"/>
+      <c r="B68" s="70"/>
       <c r="C68" s="2">
         <v>8</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E68" s="3">
         <v>5</v>
@@ -6800,16 +7282,16 @@
         <v>0</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B69" s="72"/>
+      <c r="B69" s="70"/>
       <c r="C69" s="2">
         <v>10</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E69" s="3">
         <v>5</v>
@@ -6818,16 +7300,16 @@
         <v>5</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B70" s="72"/>
+      <c r="B70" s="70"/>
       <c r="C70" s="2">
         <v>8</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E70" s="3">
         <v>15</v>
@@ -6836,16 +7318,16 @@
         <v>0</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B71" s="73"/>
+      <c r="B71" s="71"/>
       <c r="C71" s="2">
         <v>9</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E71" s="3">
         <v>10</v>
@@ -6854,7 +7336,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.25">
@@ -6890,29 +7372,29 @@
         <v>50</v>
       </c>
       <c r="G73" s="34" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="77" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B77" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C77" s="66"/>
-      <c r="D77" s="66"/>
-      <c r="E77" s="66"/>
-      <c r="F77" s="66"/>
-      <c r="G77" s="67"/>
+        <v>127</v>
+      </c>
+      <c r="C77" s="62"/>
+      <c r="D77" s="62"/>
+      <c r="E77" s="62"/>
+      <c r="F77" s="62"/>
+      <c r="G77" s="63"/>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B78" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="69"/>
-      <c r="D78" s="69"/>
-      <c r="E78" s="69"/>
-      <c r="F78" s="69"/>
-      <c r="G78" s="70"/>
+      <c r="B78" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="65"/>
+      <c r="D78" s="65"/>
+      <c r="E78" s="65"/>
+      <c r="F78" s="65"/>
+      <c r="G78" s="66"/>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B79" s="9" t="s">
@@ -6960,7 +7442,7 @@
         <v>81</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E81" s="3">
         <v>10</v>
@@ -6969,11 +7451,11 @@
         <v>0</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="71" t="s">
+      <c r="B82" s="69" t="s">
         <v>78</v>
       </c>
       <c r="C82" s="27">
@@ -6991,12 +7473,12 @@
       <c r="G82" s="22"/>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B83" s="63"/>
+      <c r="B83" s="68"/>
       <c r="C83" s="24">
         <v>4</v>
       </c>
       <c r="D83" s="29" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E83" s="29">
         <v>10</v>
@@ -7007,14 +7489,14 @@
       <c r="G83" s="22"/>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B84" s="55" t="s">
+      <c r="B84" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C84" s="23">
         <v>5</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E84" s="3">
         <v>5</v>
@@ -7025,12 +7507,12 @@
       <c r="G84" s="11"/>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B85" s="72"/>
+      <c r="B85" s="70"/>
       <c r="C85" s="23">
         <v>6</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E85" s="3">
         <v>5</v>
@@ -7041,12 +7523,12 @@
       <c r="G85" s="11"/>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B86" s="72"/>
+      <c r="B86" s="70"/>
       <c r="C86" s="2">
         <v>7</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E86" s="3">
         <v>5</v>
@@ -7057,12 +7539,12 @@
       <c r="G86" s="11"/>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B87" s="72"/>
+      <c r="B87" s="70"/>
       <c r="C87" s="2">
         <v>8</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E87" s="3">
         <v>5</v>
@@ -7073,12 +7555,12 @@
       <c r="G87" s="11"/>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B88" s="72"/>
+      <c r="B88" s="70"/>
       <c r="C88" s="2">
         <v>10</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E88" s="3">
         <v>5</v>
@@ -7089,12 +7571,12 @@
       <c r="G88" s="11"/>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B89" s="72"/>
+      <c r="B89" s="70"/>
       <c r="C89" s="2">
         <v>8</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E89" s="3">
         <v>15</v>
@@ -7105,12 +7587,12 @@
       <c r="G89" s="11"/>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B90" s="73"/>
+      <c r="B90" s="71"/>
       <c r="C90" s="2">
         <v>9</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E90" s="3">
         <v>10</v>
@@ -7119,7 +7601,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.25">
@@ -7155,29 +7637,29 @@
         <v>80</v>
       </c>
       <c r="G92" s="35" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="95" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B96" s="46" t="s">
-        <v>139</v>
-      </c>
-      <c r="C96" s="66"/>
-      <c r="D96" s="66"/>
-      <c r="E96" s="66"/>
-      <c r="F96" s="66"/>
-      <c r="G96" s="67"/>
+        <v>132</v>
+      </c>
+      <c r="C96" s="62"/>
+      <c r="D96" s="62"/>
+      <c r="E96" s="62"/>
+      <c r="F96" s="62"/>
+      <c r="G96" s="63"/>
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B97" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97" s="69"/>
-      <c r="D97" s="69"/>
-      <c r="E97" s="69"/>
-      <c r="F97" s="69"/>
-      <c r="G97" s="70"/>
+      <c r="B97" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="65"/>
+      <c r="D97" s="65"/>
+      <c r="E97" s="65"/>
+      <c r="F97" s="65"/>
+      <c r="G97" s="66"/>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B98" s="9" t="s">
@@ -7225,7 +7707,7 @@
         <v>81</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E100" s="3">
         <v>10</v>
@@ -7236,7 +7718,7 @@
       <c r="G100" s="11"/>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B101" s="71" t="s">
+      <c r="B101" s="69" t="s">
         <v>78</v>
       </c>
       <c r="C101" s="27">
@@ -7254,12 +7736,12 @@
       <c r="G101" s="22"/>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B102" s="63"/>
+      <c r="B102" s="68"/>
       <c r="C102" s="24">
         <v>4</v>
       </c>
       <c r="D102" s="29" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E102" s="29">
         <v>10</v>
@@ -7270,14 +7752,14 @@
       <c r="G102" s="22"/>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B103" s="55" t="s">
+      <c r="B103" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C103" s="23">
         <v>5</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E103" s="3">
         <v>5</v>
@@ -7288,12 +7770,12 @@
       <c r="G103" s="11"/>
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B104" s="72"/>
+      <c r="B104" s="70"/>
       <c r="C104" s="23">
         <v>6</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E104" s="3">
         <v>5</v>
@@ -7304,12 +7786,12 @@
       <c r="G104" s="11"/>
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B105" s="72"/>
+      <c r="B105" s="70"/>
       <c r="C105" s="2">
         <v>7</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E105" s="3">
         <v>5</v>
@@ -7318,16 +7800,16 @@
         <v>0</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B106" s="72"/>
+      <c r="B106" s="70"/>
       <c r="C106" s="2">
         <v>8</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E106" s="3">
         <v>5</v>
@@ -7338,12 +7820,12 @@
       <c r="G106" s="11"/>
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B107" s="72"/>
+      <c r="B107" s="70"/>
       <c r="C107" s="2">
         <v>10</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E107" s="3">
         <v>5</v>
@@ -7354,12 +7836,12 @@
       <c r="G107" s="11"/>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B108" s="72"/>
+      <c r="B108" s="70"/>
       <c r="C108" s="2">
         <v>8</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E108" s="3">
         <v>15</v>
@@ -7370,12 +7852,12 @@
       <c r="G108" s="11"/>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B109" s="73"/>
+      <c r="B109" s="71"/>
       <c r="C109" s="2">
         <v>9</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E109" s="3">
         <v>10</v>
@@ -7384,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.25">
@@ -7420,41 +7902,41 @@
         <v>85</v>
       </c>
       <c r="G111" s="35" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B96:G96"/>
+    <mergeCell ref="B97:G97"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="B103:B109"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B35"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="B78:G78"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="B84:B90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B59:G59"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B65:B71"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B47:B53"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B40:G40"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B16"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B41:G41"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B47:B53"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B59:G59"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B65:B71"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="B78:G78"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B84:B90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B35"/>
-    <mergeCell ref="B96:G96"/>
-    <mergeCell ref="B97:G97"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="B103:B109"/>
-    <mergeCell ref="B111:D111"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7479,7 +7961,7 @@
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="46" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C3" s="47"/>
       <c r="D3" s="48"/>
@@ -7488,14 +7970,14 @@
       <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
+      <c r="B4" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -7534,7 +8016,7 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="23" t="s">
@@ -7550,7 +8032,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="65"/>
+      <c r="B8" s="73"/>
       <c r="C8" s="23" t="s">
         <v>89</v>
       </c>
@@ -7564,7 +8046,7 @@
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C9" s="27">
@@ -7580,7 +8062,7 @@
       <c r="G9" s="22"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="54"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="24">
         <v>5</v>
       </c>
@@ -7594,7 +8076,7 @@
       <c r="G10" s="22"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C11" s="23">
@@ -7610,7 +8092,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -7624,7 +8106,7 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="55"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -7638,7 +8120,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="55"/>
+      <c r="B14" s="56"/>
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -7652,7 +8134,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="55"/>
+      <c r="B15" s="56"/>
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -7682,11 +8164,11 @@
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="58"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="52"/>
       <c r="E17" s="10">
         <f>SUM(E6:E16)</f>
         <v>100</v>
@@ -7700,7 +8182,7 @@
     <row r="20" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="46" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C21" s="47"/>
       <c r="D21" s="48"/>
@@ -7709,14 +8191,14 @@
       <c r="G21" s="49"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="52"/>
+      <c r="B22" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="55"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
@@ -7757,7 +8239,7 @@
       <c r="G24" s="15"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="64" t="s">
+      <c r="B25" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C25" s="23" t="s">
@@ -7775,7 +8257,7 @@
       <c r="G25" s="11"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="65"/>
+      <c r="B26" s="73"/>
       <c r="C26" s="23" t="s">
         <v>89</v>
       </c>
@@ -7789,11 +8271,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="53" t="s">
+      <c r="B27" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C27" s="27">
@@ -7811,7 +8293,7 @@
       <c r="G27" s="22"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="54"/>
+      <c r="B28" s="58"/>
       <c r="C28" s="24">
         <v>5</v>
       </c>
@@ -7825,11 +8307,11 @@
         <v>5</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C29" s="23">
@@ -7845,11 +8327,11 @@
         <v>0</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="55"/>
+      <c r="B30" s="56"/>
       <c r="C30" s="2">
         <v>7</v>
       </c>
@@ -7863,11 +8345,11 @@
         <v>0</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="55"/>
+      <c r="B31" s="56"/>
       <c r="C31" s="2">
         <v>8</v>
       </c>
@@ -7881,11 +8363,11 @@
         <v>0</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="55"/>
+      <c r="B32" s="56"/>
       <c r="C32" s="2">
         <v>9</v>
       </c>
@@ -7901,7 +8383,7 @@
       <c r="G32" s="11"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="55"/>
+      <c r="B33" s="56"/>
       <c r="C33" s="2">
         <v>10</v>
       </c>
@@ -7935,11 +8417,11 @@
       <c r="G34" s="15"/>
     </row>
     <row r="35" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="56" t="s">
+      <c r="B35" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="58"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="52"/>
       <c r="E35" s="10">
         <f>SUM(E24:E34)</f>
         <v>100</v>
@@ -7949,13 +8431,13 @@
         <v>56</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="46" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C38" s="47"/>
       <c r="D38" s="48"/>
@@ -7964,14 +8446,14 @@
       <c r="G38" s="49"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="52"/>
+      <c r="B39" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="55"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
@@ -8012,7 +8494,7 @@
       <c r="G41" s="15"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="64" t="s">
+      <c r="B42" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C42" s="23" t="s">
@@ -8030,7 +8512,7 @@
       <c r="G42" s="11"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="65"/>
+      <c r="B43" s="73"/>
       <c r="C43" s="23" t="s">
         <v>89</v>
       </c>
@@ -8046,7 +8528,7 @@
       <c r="G43" s="11"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="53" t="s">
+      <c r="B44" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C44" s="27">
@@ -8064,7 +8546,7 @@
       <c r="G44" s="22"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="54"/>
+      <c r="B45" s="58"/>
       <c r="C45" s="24">
         <v>5</v>
       </c>
@@ -8078,11 +8560,11 @@
         <v>0</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="55" t="s">
+      <c r="B46" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C46" s="23">
@@ -8098,11 +8580,11 @@
         <v>0</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="55"/>
+      <c r="B47" s="56"/>
       <c r="C47" s="2">
         <v>7</v>
       </c>
@@ -8118,7 +8600,7 @@
       <c r="G47" s="11"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="55"/>
+      <c r="B48" s="56"/>
       <c r="C48" s="2">
         <v>8</v>
       </c>
@@ -8134,7 +8616,7 @@
       <c r="G48" s="11"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="55"/>
+      <c r="B49" s="56"/>
       <c r="C49" s="2">
         <v>9</v>
       </c>
@@ -8150,7 +8632,7 @@
       <c r="G49" s="11"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="55"/>
+      <c r="B50" s="56"/>
       <c r="C50" s="2">
         <v>10</v>
       </c>
@@ -8184,11 +8666,11 @@
       <c r="G51" s="15"/>
     </row>
     <row r="52" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="56" t="s">
+      <c r="B52" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C52" s="57"/>
-      <c r="D52" s="58"/>
+      <c r="C52" s="51"/>
+      <c r="D52" s="52"/>
       <c r="E52" s="10">
         <f>SUM(E41:E51)</f>
         <v>100</v>
@@ -8198,13 +8680,13 @@
         <v>84</v>
       </c>
       <c r="G52" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="46" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C56" s="47"/>
       <c r="D56" s="48"/>
@@ -8213,14 +8695,14 @@
       <c r="G56" s="49"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="51"/>
-      <c r="D57" s="51"/>
-      <c r="E57" s="51"/>
-      <c r="F57" s="51"/>
-      <c r="G57" s="52"/>
+      <c r="B57" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="55"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="9" t="s">
@@ -8261,7 +8743,7 @@
       <c r="G59" s="15"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B60" s="64" t="s">
+      <c r="B60" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C60" s="23" t="s">
@@ -8279,7 +8761,7 @@
       <c r="G60" s="11"/>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B61" s="65"/>
+      <c r="B61" s="73"/>
       <c r="C61" s="23" t="s">
         <v>89</v>
       </c>
@@ -8295,7 +8777,7 @@
       <c r="G61" s="11"/>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B62" s="53" t="s">
+      <c r="B62" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C62" s="27">
@@ -8313,7 +8795,7 @@
       <c r="G62" s="22"/>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B63" s="54"/>
+      <c r="B63" s="58"/>
       <c r="C63" s="24">
         <v>5</v>
       </c>
@@ -8329,7 +8811,7 @@
       <c r="G63" s="22"/>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B64" s="55" t="s">
+      <c r="B64" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C64" s="23">
@@ -8345,11 +8827,11 @@
         <v>0</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B65" s="55"/>
+      <c r="B65" s="56"/>
       <c r="C65" s="2">
         <v>7</v>
       </c>
@@ -8363,11 +8845,11 @@
         <v>0</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="55"/>
+      <c r="B66" s="56"/>
       <c r="C66" s="2">
         <v>8</v>
       </c>
@@ -8381,11 +8863,11 @@
         <v>0</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B67" s="55"/>
+      <c r="B67" s="56"/>
       <c r="C67" s="2">
         <v>9</v>
       </c>
@@ -8399,11 +8881,11 @@
         <v>0</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B68" s="55"/>
+      <c r="B68" s="56"/>
       <c r="C68" s="2">
         <v>10</v>
       </c>
@@ -8417,7 +8899,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.25">
@@ -8437,15 +8919,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="15" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="56" t="s">
+      <c r="B70" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="57"/>
-      <c r="D70" s="58"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="52"/>
       <c r="E70" s="10">
         <f>SUM(E59:E69)</f>
         <v>100</v>
@@ -8455,18 +8937,18 @@
         <v>45</v>
       </c>
       <c r="G70" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F71" s="40" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="75" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B75" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C75" s="47"/>
       <c r="D75" s="48"/>
@@ -8475,14 +8957,14 @@
       <c r="G75" s="49"/>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B76" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="51"/>
-      <c r="D76" s="51"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="51"/>
-      <c r="G76" s="52"/>
+      <c r="B76" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="54"/>
+      <c r="D76" s="54"/>
+      <c r="E76" s="54"/>
+      <c r="F76" s="54"/>
+      <c r="G76" s="55"/>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B77" s="9" t="s">
@@ -8523,7 +9005,7 @@
       <c r="G78" s="15"/>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B79" s="64" t="s">
+      <c r="B79" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C79" s="23" t="s">
@@ -8539,11 +9021,11 @@
         <v>0</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B80" s="65"/>
+      <c r="B80" s="73"/>
       <c r="C80" s="23" t="s">
         <v>89</v>
       </c>
@@ -8557,11 +9039,11 @@
         <v>0</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B81" s="53" t="s">
+      <c r="B81" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C81" s="27">
@@ -8579,7 +9061,7 @@
       <c r="G81" s="22"/>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="54"/>
+      <c r="B82" s="58"/>
       <c r="C82" s="24">
         <v>5</v>
       </c>
@@ -8593,11 +9075,11 @@
         <v>0</v>
       </c>
       <c r="G82" s="22" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B83" s="55" t="s">
+      <c r="B83" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C83" s="23">
@@ -8613,11 +9095,11 @@
         <v>0</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B84" s="55"/>
+      <c r="B84" s="56"/>
       <c r="C84" s="2">
         <v>7</v>
       </c>
@@ -8631,11 +9113,11 @@
         <v>0</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B85" s="55"/>
+      <c r="B85" s="56"/>
       <c r="C85" s="2">
         <v>8</v>
       </c>
@@ -8651,7 +9133,7 @@
       <c r="G85" s="11"/>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B86" s="55"/>
+      <c r="B86" s="56"/>
       <c r="C86" s="2">
         <v>9</v>
       </c>
@@ -8665,11 +9147,11 @@
         <v>0</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B87" s="55"/>
+      <c r="B87" s="56"/>
       <c r="C87" s="2">
         <v>10</v>
       </c>
@@ -8683,7 +9165,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.25">
@@ -8703,15 +9185,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="22" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="89" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="56" t="s">
+      <c r="B89" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C89" s="57"/>
-      <c r="D89" s="58"/>
+      <c r="C89" s="51"/>
+      <c r="D89" s="52"/>
       <c r="E89" s="10">
         <f>SUM(E78:E88)</f>
         <v>100</v>
@@ -8721,13 +9203,13 @@
         <v>31</v>
       </c>
       <c r="G89" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B94" s="46" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C94" s="47"/>
       <c r="D94" s="48"/>
@@ -8736,14 +9218,14 @@
       <c r="G94" s="49"/>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B95" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="51"/>
-      <c r="D95" s="51"/>
-      <c r="E95" s="51"/>
-      <c r="F95" s="51"/>
-      <c r="G95" s="52"/>
+      <c r="B95" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="54"/>
+      <c r="D95" s="54"/>
+      <c r="E95" s="54"/>
+      <c r="F95" s="54"/>
+      <c r="G95" s="55"/>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B96" s="9" t="s">
@@ -8784,7 +9266,7 @@
       <c r="G97" s="15"/>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B98" s="64" t="s">
+      <c r="B98" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C98" s="23" t="s">
@@ -8802,7 +9284,7 @@
       <c r="G98" s="11"/>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B99" s="65"/>
+      <c r="B99" s="73"/>
       <c r="C99" s="23" t="s">
         <v>89</v>
       </c>
@@ -8818,7 +9300,7 @@
       <c r="G99" s="11"/>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B100" s="53" t="s">
+      <c r="B100" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C100" s="27">
@@ -8834,11 +9316,11 @@
         <v>0</v>
       </c>
       <c r="G100" s="22" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B101" s="54"/>
+      <c r="B101" s="58"/>
       <c r="C101" s="24">
         <v>5</v>
       </c>
@@ -8854,7 +9336,7 @@
       <c r="G101" s="22"/>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B102" s="55" t="s">
+      <c r="B102" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C102" s="23">
@@ -8870,11 +9352,11 @@
         <v>0</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B103" s="55"/>
+      <c r="B103" s="56"/>
       <c r="C103" s="2">
         <v>7</v>
       </c>
@@ -8888,11 +9370,11 @@
         <v>0</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B104" s="55"/>
+      <c r="B104" s="56"/>
       <c r="C104" s="2">
         <v>8</v>
       </c>
@@ -8906,11 +9388,11 @@
         <v>0</v>
       </c>
       <c r="G104" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B105" s="55"/>
+      <c r="B105" s="56"/>
       <c r="C105" s="2">
         <v>9</v>
       </c>
@@ -8924,11 +9406,11 @@
         <v>0</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B106" s="55"/>
+      <c r="B106" s="56"/>
       <c r="C106" s="2">
         <v>10</v>
       </c>
@@ -8960,15 +9442,15 @@
         <v>0</v>
       </c>
       <c r="G107" s="22" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="108" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="56" t="s">
+      <c r="B108" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C108" s="57"/>
-      <c r="D108" s="58"/>
+      <c r="C108" s="51"/>
+      <c r="D108" s="52"/>
       <c r="E108" s="10">
         <f>SUM(E97:E107)</f>
         <v>100</v>
@@ -8978,47 +9460,47 @@
         <v>51</v>
       </c>
       <c r="G108" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B95:G95"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="B102:B106"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="B83:B87"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="B94:G94"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B64:B68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B46:B50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B33"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B15"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B46:B50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B64:B68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="B83:B87"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B94:G94"/>
+    <mergeCell ref="B95:G95"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="B102:B106"/>
+    <mergeCell ref="B108:D108"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9043,7 +9525,7 @@
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="46" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C3" s="47"/>
       <c r="D3" s="48"/>
@@ -9052,14 +9534,14 @@
       <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
+      <c r="B4" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -9098,14 +9580,14 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>81</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E7" s="3">
         <v>5</v>
@@ -9114,12 +9596,12 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="65"/>
+      <c r="B8" s="73"/>
       <c r="C8" s="23" t="s">
         <v>96</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E8" s="3">
         <v>5</v>
@@ -9128,7 +9610,7 @@
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C9" s="25">
@@ -9149,7 +9631,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E10" s="29">
         <v>5</v>
@@ -9158,14 +9640,14 @@
       <c r="G10" s="22"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C11" s="23">
         <v>6</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E11" s="3">
         <v>10</v>
@@ -9174,12 +9656,12 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="23">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E12" s="3">
         <v>10</v>
@@ -9188,12 +9670,12 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="55"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="23">
         <v>8</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E13" s="3">
         <v>10</v>
@@ -9202,12 +9684,12 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="55"/>
+      <c r="B14" s="56"/>
       <c r="C14" s="2">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E14" s="3">
         <v>15</v>
@@ -9248,11 +9730,11 @@
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="58"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="52"/>
       <c r="E17" s="10">
         <f>SUM(E6:E16)</f>
         <v>100</v>
@@ -9262,13 +9744,13 @@
         <v>0</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="46" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C21" s="47"/>
       <c r="D21" s="48"/>
@@ -9277,14 +9759,14 @@
       <c r="G21" s="49"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="52"/>
+      <c r="B22" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="55"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
@@ -9325,14 +9807,14 @@
       <c r="G24" s="15"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="64" t="s">
+      <c r="B25" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C25" s="23" t="s">
         <v>81</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E25" s="3">
         <v>5</v>
@@ -9343,12 +9825,12 @@
       <c r="G25" s="11"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="65"/>
+      <c r="B26" s="73"/>
       <c r="C26" s="23" t="s">
         <v>96</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E26" s="3">
         <v>5</v>
@@ -9359,7 +9841,7 @@
       <c r="G26" s="11"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="53" t="s">
+      <c r="B27" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C27" s="25">
@@ -9382,7 +9864,7 @@
         <v>4</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E28" s="29">
         <v>5</v>
@@ -9393,14 +9875,14 @@
       <c r="G28" s="22"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C29" s="23">
         <v>6</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E29" s="3">
         <v>10</v>
@@ -9411,12 +9893,12 @@
       <c r="G29" s="11"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="55"/>
+      <c r="B30" s="56"/>
       <c r="C30" s="23">
         <v>7</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E30" s="3">
         <v>10</v>
@@ -9427,12 +9909,12 @@
       <c r="G30" s="11"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="55"/>
+      <c r="B31" s="56"/>
       <c r="C31" s="23">
         <v>8</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E31" s="3">
         <v>10</v>
@@ -9441,16 +9923,16 @@
         <v>5</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="55"/>
+      <c r="B32" s="56"/>
       <c r="C32" s="2">
         <v>9</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E32" s="3">
         <v>15</v>
@@ -9497,11 +9979,11 @@
       <c r="G34" s="11"/>
     </row>
     <row r="35" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="56" t="s">
+      <c r="B35" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="58"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="52"/>
       <c r="E35" s="10">
         <f>SUM(E24:E34)</f>
         <v>100</v>
@@ -9511,13 +9993,13 @@
         <v>95</v>
       </c>
       <c r="G35" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="46" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C38" s="47"/>
       <c r="D38" s="48"/>
@@ -9526,14 +10008,14 @@
       <c r="G38" s="49"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="52"/>
+      <c r="B39" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="55"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
@@ -9574,14 +10056,14 @@
       <c r="G41" s="15"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="64" t="s">
+      <c r="B42" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C42" s="23" t="s">
         <v>81</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E42" s="3">
         <v>5</v>
@@ -9590,16 +10072,16 @@
         <v>0</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="65"/>
+      <c r="B43" s="73"/>
       <c r="C43" s="23" t="s">
         <v>96</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E43" s="3">
         <v>5</v>
@@ -9608,11 +10090,11 @@
         <v>2.5</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="53" t="s">
+      <c r="B44" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C44" s="25">
@@ -9635,7 +10117,7 @@
         <v>4</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E45" s="29">
         <v>5</v>
@@ -9644,18 +10126,18 @@
         <v>2.5</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="55" t="s">
+      <c r="B46" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C46" s="23">
         <v>6</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E46" s="3">
         <v>10</v>
@@ -9666,12 +10148,12 @@
       <c r="G46" s="11"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="55"/>
+      <c r="B47" s="56"/>
       <c r="C47" s="23">
         <v>7</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E47" s="3">
         <v>10</v>
@@ -9682,12 +10164,12 @@
       <c r="G47" s="11"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="55"/>
+      <c r="B48" s="56"/>
       <c r="C48" s="23">
         <v>8</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E48" s="3">
         <v>10</v>
@@ -9698,12 +10180,12 @@
       <c r="G48" s="11"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="55"/>
+      <c r="B49" s="56"/>
       <c r="C49" s="2">
         <v>9</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E49" s="3">
         <v>15</v>
@@ -9750,11 +10232,11 @@
       <c r="G51" s="11"/>
     </row>
     <row r="52" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="56" t="s">
+      <c r="B52" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C52" s="57"/>
-      <c r="D52" s="58"/>
+      <c r="C52" s="51"/>
+      <c r="D52" s="52"/>
       <c r="E52" s="10">
         <f>SUM(E41:E51)</f>
         <v>100</v>
@@ -9764,13 +10246,13 @@
         <v>90</v>
       </c>
       <c r="G52" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="46" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C56" s="47"/>
       <c r="D56" s="48"/>
@@ -9779,14 +10261,14 @@
       <c r="G56" s="49"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="51"/>
-      <c r="D57" s="51"/>
-      <c r="E57" s="51"/>
-      <c r="F57" s="51"/>
-      <c r="G57" s="52"/>
+      <c r="B57" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="55"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="9" t="s">
@@ -9827,14 +10309,14 @@
       <c r="G59" s="15"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B60" s="64" t="s">
+      <c r="B60" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C60" s="23" t="s">
         <v>81</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E60" s="3">
         <v>5</v>
@@ -9845,12 +10327,12 @@
       <c r="G60" s="11"/>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B61" s="65"/>
+      <c r="B61" s="73"/>
       <c r="C61" s="23" t="s">
         <v>96</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E61" s="3">
         <v>5</v>
@@ -9861,7 +10343,7 @@
       <c r="G61" s="11"/>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B62" s="53" t="s">
+      <c r="B62" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C62" s="25">
@@ -9884,7 +10366,7 @@
         <v>4</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E63" s="29">
         <v>5</v>
@@ -9893,18 +10375,18 @@
         <v>2.5</v>
       </c>
       <c r="G63" s="22" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B64" s="55" t="s">
+      <c r="B64" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C64" s="23">
         <v>6</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E64" s="3">
         <v>10</v>
@@ -9915,12 +10397,12 @@
       <c r="G64" s="11"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B65" s="55"/>
+      <c r="B65" s="56"/>
       <c r="C65" s="23">
         <v>7</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E65" s="3">
         <v>10</v>
@@ -9929,16 +10411,16 @@
         <v>0</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="55"/>
+      <c r="B66" s="56"/>
       <c r="C66" s="23">
         <v>8</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E66" s="3">
         <v>10</v>
@@ -9949,12 +10431,12 @@
       <c r="G66" s="11"/>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B67" s="55"/>
+      <c r="B67" s="56"/>
       <c r="C67" s="2">
         <v>9</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E67" s="3">
         <v>15</v>
@@ -9999,15 +10481,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="56" t="s">
+      <c r="B70" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="57"/>
-      <c r="D70" s="58"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="52"/>
       <c r="E70" s="10">
         <f>SUM(E59:E69)</f>
         <v>100</v>
@@ -10017,13 +10499,13 @@
         <v>72.5</v>
       </c>
       <c r="G70" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="73" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="74" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B74" s="46" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C74" s="47"/>
       <c r="D74" s="48"/>
@@ -10032,14 +10514,14 @@
       <c r="G74" s="49"/>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B75" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="51"/>
-      <c r="G75" s="52"/>
+      <c r="B75" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="54"/>
+      <c r="D75" s="54"/>
+      <c r="E75" s="54"/>
+      <c r="F75" s="54"/>
+      <c r="G75" s="55"/>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B76" s="9" t="s">
@@ -10080,14 +10562,14 @@
       <c r="G77" s="15"/>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B78" s="64" t="s">
+      <c r="B78" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C78" s="23" t="s">
         <v>81</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E78" s="3">
         <v>5</v>
@@ -10098,12 +10580,12 @@
       <c r="G78" s="11"/>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B79" s="65"/>
+      <c r="B79" s="73"/>
       <c r="C79" s="23" t="s">
         <v>96</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E79" s="3">
         <v>5</v>
@@ -10114,7 +10596,7 @@
       <c r="G79" s="11"/>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B80" s="53" t="s">
+      <c r="B80" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C80" s="25">
@@ -10137,7 +10619,7 @@
         <v>4</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E81" s="29">
         <v>5</v>
@@ -10148,14 +10630,14 @@
       <c r="G81" s="22"/>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="55" t="s">
+      <c r="B82" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C82" s="23">
         <v>6</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E82" s="3">
         <v>10</v>
@@ -10164,16 +10646,16 @@
         <v>0</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B83" s="55"/>
+      <c r="B83" s="56"/>
       <c r="C83" s="23">
         <v>7</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E83" s="3">
         <v>10</v>
@@ -10184,12 +10666,12 @@
       <c r="G83" s="11"/>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B84" s="55"/>
+      <c r="B84" s="56"/>
       <c r="C84" s="23">
         <v>8</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E84" s="3">
         <v>10</v>
@@ -10198,16 +10680,16 @@
         <v>0</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B85" s="55"/>
+      <c r="B85" s="56"/>
       <c r="C85" s="2">
         <v>9</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E85" s="3">
         <v>15</v>
@@ -10216,7 +10698,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.25">
@@ -10254,15 +10736,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="88" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B88" s="56" t="s">
+      <c r="B88" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C88" s="57"/>
-      <c r="D88" s="58"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="52"/>
       <c r="E88" s="10">
         <f>SUM(E77:E87)</f>
         <v>100</v>
@@ -10272,13 +10754,13 @@
         <v>50</v>
       </c>
       <c r="G88" s="34" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="91" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="92" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B92" s="46" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C92" s="47"/>
       <c r="D92" s="48"/>
@@ -10287,14 +10769,14 @@
       <c r="G92" s="49"/>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B93" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="51"/>
-      <c r="D93" s="51"/>
-      <c r="E93" s="51"/>
-      <c r="F93" s="51"/>
-      <c r="G93" s="52"/>
+      <c r="B93" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="54"/>
+      <c r="D93" s="54"/>
+      <c r="E93" s="54"/>
+      <c r="F93" s="54"/>
+      <c r="G93" s="55"/>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B94" s="9" t="s">
@@ -10333,18 +10815,18 @@
         <v>10</v>
       </c>
       <c r="G95" s="15" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B96" s="64" t="s">
+      <c r="B96" s="72" t="s">
         <v>71</v>
       </c>
       <c r="C96" s="23" t="s">
         <v>81</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E96" s="3">
         <v>5</v>
@@ -10355,12 +10837,12 @@
       <c r="G96" s="11"/>
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B97" s="65"/>
+      <c r="B97" s="73"/>
       <c r="C97" s="23" t="s">
         <v>96</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E97" s="3">
         <v>5</v>
@@ -10371,7 +10853,7 @@
       <c r="G97" s="11"/>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B98" s="53" t="s">
+      <c r="B98" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C98" s="25">
@@ -10387,7 +10869,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="22" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.25">
@@ -10396,7 +10878,7 @@
         <v>4</v>
       </c>
       <c r="D99" s="29" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E99" s="29">
         <v>5</v>
@@ -10407,14 +10889,14 @@
       <c r="G99" s="22"/>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B100" s="55" t="s">
+      <c r="B100" s="56" t="s">
         <v>75</v>
       </c>
       <c r="C100" s="23">
         <v>6</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E100" s="3">
         <v>10</v>
@@ -10425,12 +10907,12 @@
       <c r="G100" s="11"/>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B101" s="55"/>
+      <c r="B101" s="56"/>
       <c r="C101" s="23">
         <v>7</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E101" s="3">
         <v>10</v>
@@ -10439,16 +10921,16 @@
         <v>0</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B102" s="55"/>
+      <c r="B102" s="56"/>
       <c r="C102" s="23">
         <v>8</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E102" s="3">
         <v>10</v>
@@ -10457,16 +10939,16 @@
         <v>0</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B103" s="55"/>
+      <c r="B103" s="56"/>
       <c r="C103" s="2">
         <v>9</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E103" s="3">
         <v>15</v>
@@ -10475,7 +10957,7 @@
         <v>10</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.25">
@@ -10495,7 +10977,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="15" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.25">
@@ -10515,15 +10997,15 @@
         <v>0</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="106" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B106" s="56" t="s">
+      <c r="B106" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C106" s="57"/>
-      <c r="D106" s="58"/>
+      <c r="C106" s="51"/>
+      <c r="D106" s="52"/>
       <c r="E106" s="10">
         <f>SUM(E95:E105)</f>
         <v>100</v>
@@ -10533,43 +11015,16 @@
         <v>45</v>
       </c>
       <c r="G106" s="34" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F107" s="40" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B64:B67"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B78:B79"/>
     <mergeCell ref="B96:B97"/>
     <mergeCell ref="B98:B99"/>
     <mergeCell ref="B100:B103"/>
@@ -10579,6 +11034,33 @@
     <mergeCell ref="B88:D88"/>
     <mergeCell ref="B92:G92"/>
     <mergeCell ref="B93:G93"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
